--- a/research/traditional_assets/database/data/singapore/singapore_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_healthcare_products.xlsx
@@ -1799,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1936,22 +1936,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09083876366469271</v>
+        <v>0.09072168776646275</v>
       </c>
       <c r="C2">
-        <v>1183.925647557868</v>
+        <v>1174.202770801088</v>
       </c>
       <c r="D2">
-        <v>992.2256475578685</v>
+        <v>994.3421908010876</v>
       </c>
       <c r="E2">
-        <v>-0.142</v>
+        <v>11.69742</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.83942</v>
       </c>
       <c r="G2">
         <v>191.7</v>
@@ -1972,28 +1972,28 @@
         <v>84.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5955228259999999</v>
       </c>
       <c r="N2">
-        <v>84.2</v>
+        <v>83.604477174</v>
       </c>
       <c r="O2">
-        <v>14.314</v>
+        <v>14.21276111958</v>
       </c>
       <c r="P2">
-        <v>69.886</v>
+        <v>69.39171605442</v>
       </c>
       <c r="Q2">
-        <v>85.28599999999999</v>
+        <v>84.79171605441999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09083876366469271</v>
+        <v>0.0912163613802654</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048876706241695</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>141.3883672025697</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2018,22 +2018,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09072168776646275</v>
+        <v>0.09060461186823278</v>
       </c>
       <c r="C3">
-        <v>1174.202770801088</v>
+        <v>1164.488943057756</v>
       </c>
       <c r="D3">
-        <v>994.3421908010876</v>
+        <v>996.467783057756</v>
       </c>
       <c r="E3">
-        <v>11.69742</v>
+        <v>23.53684</v>
       </c>
       <c r="F3">
-        <v>11.83942</v>
+        <v>23.67884</v>
       </c>
       <c r="G3">
         <v>191.7</v>
@@ -2054,28 +2054,28 @@
         <v>84.2</v>
       </c>
       <c r="M3">
-        <v>0.5955228259999999</v>
+        <v>1.191045652</v>
       </c>
       <c r="N3">
-        <v>83.604477174</v>
+        <v>83.008954348</v>
       </c>
       <c r="O3">
-        <v>14.21276111958</v>
+        <v>14.11152223916</v>
       </c>
       <c r="P3">
-        <v>69.39171605442</v>
+        <v>68.89743210884001</v>
       </c>
       <c r="Q3">
-        <v>84.79171605441999</v>
+        <v>84.29743210884</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0912163613802654</v>
+        <v>0.0916016651716661</v>
       </c>
       <c r="T3">
-        <v>1.048876706241695</v>
+        <v>1.057775177174736</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>141.3883672025697</v>
+        <v>70.69418360128483</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2100,22 +2100,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09060461186823278</v>
+        <v>0.09048753597000278</v>
       </c>
       <c r="C4">
-        <v>1164.488943057756</v>
+        <v>1154.784222484065</v>
       </c>
       <c r="D4">
-        <v>996.467783057756</v>
+        <v>998.6024824840654</v>
       </c>
       <c r="E4">
-        <v>23.53684</v>
+        <v>35.37625999999999</v>
       </c>
       <c r="F4">
-        <v>23.67884</v>
+        <v>35.51826</v>
       </c>
       <c r="G4">
         <v>191.7</v>
@@ -2136,28 +2136,28 @@
         <v>84.2</v>
       </c>
       <c r="M4">
-        <v>1.191045652</v>
+        <v>1.786568478</v>
       </c>
       <c r="N4">
-        <v>83.008954348</v>
+        <v>82.413431522</v>
       </c>
       <c r="O4">
-        <v>14.11152223916</v>
+        <v>14.01028335874</v>
       </c>
       <c r="P4">
-        <v>68.89743210884001</v>
+        <v>68.40314816326</v>
       </c>
       <c r="Q4">
-        <v>84.29743210884</v>
+        <v>83.80314816325999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0916016651716661</v>
+        <v>0.09199491337113688</v>
       </c>
       <c r="T4">
-        <v>1.057775177174736</v>
+        <v>1.066857121735263</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.69418360128483</v>
+        <v>47.12945573418989</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2182,22 +2182,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09048753597000278</v>
+        <v>0.0903704600717728</v>
       </c>
       <c r="C5">
-        <v>1154.784222484065</v>
+        <v>1145.088667735621</v>
       </c>
       <c r="D5">
-        <v>998.6024824840654</v>
+        <v>1000.746347735621</v>
       </c>
       <c r="E5">
-        <v>35.37625999999999</v>
+        <v>47.21568</v>
       </c>
       <c r="F5">
-        <v>35.51826</v>
+        <v>47.35768</v>
       </c>
       <c r="G5">
         <v>191.7</v>
@@ -2218,28 +2218,28 @@
         <v>84.2</v>
       </c>
       <c r="M5">
-        <v>1.786568478</v>
+        <v>2.382091304</v>
       </c>
       <c r="N5">
-        <v>82.413431522</v>
+        <v>81.817908696</v>
       </c>
       <c r="O5">
-        <v>14.01028335874</v>
+        <v>13.90904447832</v>
       </c>
       <c r="P5">
-        <v>68.40314816326</v>
+        <v>67.90886421768001</v>
       </c>
       <c r="Q5">
-        <v>83.80314816325999</v>
+        <v>83.30886421768</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09199491337113688</v>
+        <v>0.09239635424143</v>
       </c>
       <c r="T5">
-        <v>1.066857121735263</v>
+        <v>1.076128273474134</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.12945573418989</v>
+        <v>35.34709180064242</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2264,22 +2264,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0903704600717728</v>
+        <v>0.09025338417354284</v>
       </c>
       <c r="C6">
-        <v>1145.088667735621</v>
+        <v>1135.402337972815</v>
       </c>
       <c r="D6">
-        <v>1000.746347735621</v>
+        <v>1002.899437972815</v>
       </c>
       <c r="E6">
-        <v>47.21568</v>
+        <v>59.0551</v>
       </c>
       <c r="F6">
-        <v>47.35768</v>
+        <v>59.19710000000001</v>
       </c>
       <c r="G6">
         <v>191.7</v>
@@ -2300,28 +2300,28 @@
         <v>84.2</v>
       </c>
       <c r="M6">
-        <v>2.382091304</v>
+        <v>2.97761413</v>
       </c>
       <c r="N6">
-        <v>81.817908696</v>
+        <v>81.22238587</v>
       </c>
       <c r="O6">
-        <v>13.90904447832</v>
+        <v>13.8078055979</v>
       </c>
       <c r="P6">
-        <v>67.90886421768001</v>
+        <v>67.4145802721</v>
       </c>
       <c r="Q6">
-        <v>83.30886421768</v>
+        <v>82.81458027209999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09239635424143</v>
+        <v>0.09280624649846614</v>
       </c>
       <c r="T6">
-        <v>1.076128273474134</v>
+        <v>1.085594607354876</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.34709180064242</v>
+        <v>28.27767344051393</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2346,22 +2346,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09025338417354284</v>
+        <v>0.09013630827531284</v>
       </c>
       <c r="C7">
-        <v>1135.402337972815</v>
+        <v>1125.725292866269</v>
       </c>
       <c r="D7">
-        <v>1002.899437972815</v>
+        <v>1005.06181286627</v>
       </c>
       <c r="E7">
-        <v>59.0551</v>
+        <v>70.89452000000001</v>
       </c>
       <c r="F7">
-        <v>59.19710000000001</v>
+        <v>71.03652000000001</v>
       </c>
       <c r="G7">
         <v>191.7</v>
@@ -2382,28 +2382,28 @@
         <v>84.2</v>
       </c>
       <c r="M7">
-        <v>2.97761413</v>
+        <v>3.573136956</v>
       </c>
       <c r="N7">
-        <v>81.22238587</v>
+        <v>80.626863044</v>
       </c>
       <c r="O7">
-        <v>13.8078055979</v>
+        <v>13.70656671748</v>
       </c>
       <c r="P7">
-        <v>67.4145802721</v>
+        <v>66.92029632652</v>
       </c>
       <c r="Q7">
-        <v>82.81458027209999</v>
+        <v>82.32029632651999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09280624649846614</v>
+        <v>0.0932248598673541</v>
       </c>
       <c r="T7">
-        <v>1.085594607354876</v>
+        <v>1.095262352594783</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.27767344051393</v>
+        <v>23.56472786709494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2428,22 +2428,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09013630827531284</v>
+        <v>0.09001923237708288</v>
       </c>
       <c r="C8">
-        <v>1125.72529286627</v>
+        <v>1116.057592602345</v>
       </c>
       <c r="D8">
-        <v>1005.06181286627</v>
+        <v>1007.233532602345</v>
       </c>
       <c r="E8">
-        <v>70.89452</v>
+        <v>82.73393999999999</v>
       </c>
       <c r="F8">
-        <v>71.03652</v>
+        <v>82.87593999999999</v>
       </c>
       <c r="G8">
         <v>191.7</v>
@@ -2464,28 +2464,28 @@
         <v>84.2</v>
       </c>
       <c r="M8">
-        <v>3.573136955999999</v>
+        <v>4.168659781999999</v>
       </c>
       <c r="N8">
-        <v>80.626863044</v>
+        <v>80.031340218</v>
       </c>
       <c r="O8">
-        <v>13.70656671748</v>
+        <v>13.60532783706</v>
       </c>
       <c r="P8">
-        <v>66.92029632652</v>
+        <v>66.42601238093999</v>
       </c>
       <c r="Q8">
-        <v>82.32029632651999</v>
+        <v>81.82601238093999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0932248598673541</v>
+        <v>0.09365247567428266</v>
       </c>
       <c r="T8">
-        <v>1.095262352594783</v>
+        <v>1.105138006334472</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.56472786709495</v>
+        <v>20.19833817179567</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2510,22 +2510,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09001923237708287</v>
+        <v>0.08990215647885288</v>
       </c>
       <c r="C9">
-        <v>1116.057592602345</v>
+        <v>1106.399297888728</v>
       </c>
       <c r="D9">
-        <v>1007.233532602345</v>
+        <v>1009.414657888728</v>
       </c>
       <c r="E9">
-        <v>82.73394000000002</v>
+        <v>94.57336000000001</v>
       </c>
       <c r="F9">
-        <v>82.87594000000001</v>
+        <v>94.71536</v>
       </c>
       <c r="G9">
         <v>191.7</v>
@@ -2546,28 +2546,28 @@
         <v>84.2</v>
       </c>
       <c r="M9">
-        <v>4.168659782000001</v>
+        <v>4.764182608</v>
       </c>
       <c r="N9">
-        <v>80.031340218</v>
+        <v>79.435817392</v>
       </c>
       <c r="O9">
-        <v>13.60532783706</v>
+        <v>13.50408895664</v>
       </c>
       <c r="P9">
-        <v>66.42601238093999</v>
+        <v>65.93172843536</v>
       </c>
       <c r="Q9">
-        <v>81.82601238093999</v>
+        <v>81.33172843535999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09365247567428266</v>
+        <v>0.09408938747701401</v>
       </c>
       <c r="T9">
-        <v>1.105138006334472</v>
+        <v>1.115228348198938</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.19833817179566</v>
+        <v>17.67354590032121</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2592,22 +2592,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08990215647885288</v>
+        <v>0.08978508058062291</v>
       </c>
       <c r="C10">
-        <v>1106.399297888728</v>
+        <v>1096.750469960087</v>
       </c>
       <c r="D10">
-        <v>1009.414657888728</v>
+        <v>1011.605249960087</v>
       </c>
       <c r="E10">
-        <v>94.57336000000001</v>
+        <v>106.41278</v>
       </c>
       <c r="F10">
-        <v>94.71536</v>
+        <v>106.55478</v>
       </c>
       <c r="G10">
         <v>191.7</v>
@@ -2628,28 +2628,28 @@
         <v>84.2</v>
       </c>
       <c r="M10">
-        <v>4.764182608</v>
+        <v>5.359705433999999</v>
       </c>
       <c r="N10">
-        <v>79.435817392</v>
+        <v>78.840294566</v>
       </c>
       <c r="O10">
-        <v>13.50408895664</v>
+        <v>13.40285007622</v>
       </c>
       <c r="P10">
-        <v>65.93172843536</v>
+        <v>65.43744448977999</v>
       </c>
       <c r="Q10">
-        <v>81.33172843535999</v>
+        <v>80.83744448977998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09408938747701401</v>
+        <v>0.09453590173694826</v>
       </c>
       <c r="T10">
-        <v>1.115228348198938</v>
+        <v>1.125540455818666</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.67354590032121</v>
+        <v>15.7098185780633</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2674,22 +2674,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08978508058062291</v>
+        <v>0.08966800468239293</v>
       </c>
       <c r="C11">
-        <v>1096.750469960087</v>
+        <v>1087.111170583803</v>
       </c>
       <c r="D11">
-        <v>1011.605249960087</v>
+        <v>1013.805370583803</v>
       </c>
       <c r="E11">
-        <v>106.41278</v>
+        <v>118.2522</v>
       </c>
       <c r="F11">
-        <v>106.55478</v>
+        <v>118.3942</v>
       </c>
       <c r="G11">
         <v>191.7</v>
@@ -2710,28 +2710,28 @@
         <v>84.2</v>
       </c>
       <c r="M11">
-        <v>5.359705433999999</v>
+        <v>5.955228259999999</v>
       </c>
       <c r="N11">
-        <v>78.840294566</v>
+        <v>78.24477174</v>
       </c>
       <c r="O11">
-        <v>13.40285007622</v>
+        <v>13.3016111958</v>
       </c>
       <c r="P11">
-        <v>65.43744448977999</v>
+        <v>64.9431605442</v>
       </c>
       <c r="Q11">
-        <v>80.83744448977998</v>
+        <v>80.34316054419999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09453590173694826</v>
+        <v>0.09499233853599215</v>
       </c>
       <c r="T11">
-        <v>1.125540455818666</v>
+        <v>1.1360817213855</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.7098185780633</v>
+        <v>14.13883672025697</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2756,22 +2756,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08966800468239293</v>
+        <v>0.08968787878416296</v>
       </c>
       <c r="C12">
-        <v>1087.111170583803</v>
+        <v>1074.897597174923</v>
       </c>
       <c r="D12">
-        <v>1013.805370583803</v>
+        <v>1013.431217174923</v>
       </c>
       <c r="E12">
-        <v>118.2522</v>
+        <v>130.09162</v>
       </c>
       <c r="F12">
-        <v>118.3942</v>
+        <v>130.23362</v>
       </c>
       <c r="G12">
         <v>191.7</v>
@@ -2792,45 +2792,45 @@
         <v>84.2</v>
       </c>
       <c r="M12">
-        <v>5.95522826</v>
+        <v>6.746101516</v>
       </c>
       <c r="N12">
-        <v>78.24477174</v>
+        <v>77.45389848400001</v>
       </c>
       <c r="O12">
-        <v>13.3016111958</v>
+        <v>13.16716274228</v>
       </c>
       <c r="P12">
-        <v>64.9431605442</v>
+        <v>64.28673574172001</v>
       </c>
       <c r="Q12">
-        <v>80.34316054419999</v>
+        <v>79.68673574172</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09499233853599215</v>
+        <v>0.09545903234175614</v>
       </c>
       <c r="T12">
-        <v>1.1360817213855</v>
+        <v>1.146859869324622</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.17</v>
       </c>
       <c r="W12">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.13883672025697</v>
+        <v>12.48128267864032</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2838,22 +2838,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08968787878416296</v>
+        <v>0.08958325288593298</v>
       </c>
       <c r="C13">
-        <v>1074.897597174923</v>
+        <v>1065.030989131207</v>
       </c>
       <c r="D13">
-        <v>1013.431217174923</v>
+        <v>1015.404029131207</v>
       </c>
       <c r="E13">
-        <v>130.09162</v>
+        <v>141.93104</v>
       </c>
       <c r="F13">
-        <v>130.23362</v>
+        <v>142.07304</v>
       </c>
       <c r="G13">
         <v>191.7</v>
@@ -2874,28 +2874,28 @@
         <v>84.2</v>
       </c>
       <c r="M13">
-        <v>6.746101516</v>
+        <v>7.359383471999999</v>
       </c>
       <c r="N13">
-        <v>77.45389848400001</v>
+        <v>76.840616528</v>
       </c>
       <c r="O13">
-        <v>13.16716274228</v>
+        <v>13.06290480976</v>
       </c>
       <c r="P13">
-        <v>64.28673574172001</v>
+        <v>63.77771171824</v>
       </c>
       <c r="Q13">
-        <v>79.68673574172</v>
+        <v>79.17771171823999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09545903234175614</v>
+        <v>0.09593633282492384</v>
       </c>
       <c r="T13">
-        <v>1.146859869324622</v>
+        <v>1.157882975171451</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.48128267864032</v>
+        <v>11.44117578875363</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2920,22 +2920,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08958325288593298</v>
+        <v>0.08947862698770302</v>
       </c>
       <c r="C14">
-        <v>1065.030989131207</v>
+        <v>1055.172076880012</v>
       </c>
       <c r="D14">
-        <v>1015.404029131207</v>
+        <v>1017.384536880012</v>
       </c>
       <c r="E14">
-        <v>141.93104</v>
+        <v>153.77046</v>
       </c>
       <c r="F14">
-        <v>142.07304</v>
+        <v>153.91246</v>
       </c>
       <c r="G14">
         <v>191.7</v>
@@ -2956,28 +2956,28 @@
         <v>84.2</v>
       </c>
       <c r="M14">
-        <v>7.359383471999999</v>
+        <v>7.972665428</v>
       </c>
       <c r="N14">
-        <v>76.840616528</v>
+        <v>76.227334572</v>
       </c>
       <c r="O14">
-        <v>13.06290480976</v>
+        <v>12.95864687724</v>
       </c>
       <c r="P14">
-        <v>63.77771171824</v>
+        <v>63.26868769476</v>
       </c>
       <c r="Q14">
-        <v>79.17771171823999</v>
+        <v>78.66868769476</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09593633282492384</v>
+        <v>0.09642460573299197</v>
       </c>
       <c r="T14">
-        <v>1.157882975171451</v>
+        <v>1.169159485750392</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.44117578875363</v>
+        <v>10.56108534346489</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3002,22 +3002,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08947862698770302</v>
+        <v>0.08957154108947304</v>
       </c>
       <c r="C15">
-        <v>1055.172076880012</v>
+        <v>1041.573463320709</v>
       </c>
       <c r="D15">
-        <v>1017.384536880012</v>
+        <v>1015.625343320709</v>
       </c>
       <c r="E15">
-        <v>153.77046</v>
+        <v>165.60988</v>
       </c>
       <c r="F15">
-        <v>153.91246</v>
+        <v>165.75188</v>
       </c>
       <c r="G15">
         <v>191.7</v>
@@ -3038,45 +3038,45 @@
         <v>84.2</v>
       </c>
       <c r="M15">
-        <v>7.972665428</v>
+        <v>8.867725580000002</v>
       </c>
       <c r="N15">
-        <v>76.227334572</v>
+        <v>75.33227442</v>
       </c>
       <c r="O15">
-        <v>12.95864687724</v>
+        <v>12.8064866514</v>
       </c>
       <c r="P15">
-        <v>63.26868769476</v>
+        <v>62.5257877686</v>
       </c>
       <c r="Q15">
-        <v>78.66868769476</v>
+        <v>77.9257877686</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09642460573299197</v>
+        <v>0.09692423382496865</v>
       </c>
       <c r="T15">
-        <v>1.169159485750392</v>
+        <v>1.1806982407614</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.17</v>
       </c>
       <c r="W15">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.56108534346489</v>
+        <v>9.495106635900205</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3084,22 +3084,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08957154108947304</v>
+        <v>0.08948102519124307</v>
       </c>
       <c r="C16">
-        <v>1041.573463320709</v>
+        <v>1031.447753762935</v>
       </c>
       <c r="D16">
-        <v>1015.625343320709</v>
+        <v>1017.339053762935</v>
       </c>
       <c r="E16">
-        <v>165.60988</v>
+        <v>177.4493</v>
       </c>
       <c r="F16">
-        <v>165.75188</v>
+        <v>177.5913</v>
       </c>
       <c r="G16">
         <v>191.7</v>
@@ -3120,28 +3120,28 @@
         <v>84.2</v>
       </c>
       <c r="M16">
-        <v>8.867725580000002</v>
+        <v>9.501134550000002</v>
       </c>
       <c r="N16">
-        <v>75.33227442</v>
+        <v>74.69886545</v>
       </c>
       <c r="O16">
-        <v>12.8064866514</v>
+        <v>12.6988071265</v>
       </c>
       <c r="P16">
-        <v>62.5257877686</v>
+        <v>62.0000583235</v>
       </c>
       <c r="Q16">
-        <v>77.9257877686</v>
+        <v>77.40005832349999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09692423382496865</v>
+        <v>0.09743561787205066</v>
       </c>
       <c r="T16">
-        <v>1.1806982407614</v>
+        <v>1.192508495890315</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.495106635900205</v>
+        <v>8.86209952684019</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3166,22 +3166,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08948102519124307</v>
+        <v>0.08939050929301307</v>
       </c>
       <c r="C17">
-        <v>1031.447753762935</v>
+        <v>1021.327837221801</v>
       </c>
       <c r="D17">
-        <v>1017.339053762935</v>
+        <v>1019.058557221801</v>
       </c>
       <c r="E17">
-        <v>177.4493</v>
+        <v>189.28872</v>
       </c>
       <c r="F17">
-        <v>177.5913</v>
+        <v>189.43072</v>
       </c>
       <c r="G17">
         <v>191.7</v>
@@ -3202,28 +3202,28 @@
         <v>84.2</v>
       </c>
       <c r="M17">
-        <v>9.50113455</v>
+        <v>10.13454352</v>
       </c>
       <c r="N17">
-        <v>74.69886545</v>
+        <v>74.06545648000001</v>
       </c>
       <c r="O17">
-        <v>12.6988071265</v>
+        <v>12.5911276016</v>
       </c>
       <c r="P17">
-        <v>62.0000583235</v>
+        <v>61.47432887840001</v>
       </c>
       <c r="Q17">
-        <v>77.40005832349999</v>
+        <v>76.87432887840001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09743561787205066</v>
+        <v>0.09795917772977747</v>
       </c>
       <c r="T17">
-        <v>1.192508495890315</v>
+        <v>1.204599947569918</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.862099526840193</v>
+        <v>8.30821830641268</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3248,22 +3248,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08939050929301307</v>
+        <v>0.08929999339478309</v>
       </c>
       <c r="C18">
-        <v>1021.327837221801</v>
+        <v>1011.213743121056</v>
       </c>
       <c r="D18">
-        <v>1019.058557221801</v>
+        <v>1020.783883121056</v>
       </c>
       <c r="E18">
-        <v>189.28872</v>
+        <v>201.12814</v>
       </c>
       <c r="F18">
-        <v>189.43072</v>
+        <v>201.27014</v>
       </c>
       <c r="G18">
         <v>191.7</v>
@@ -3284,28 +3284,28 @@
         <v>84.2</v>
       </c>
       <c r="M18">
-        <v>10.13454352</v>
+        <v>10.76795249</v>
       </c>
       <c r="N18">
-        <v>74.06545648000001</v>
+        <v>73.43204751</v>
       </c>
       <c r="O18">
-        <v>12.5911276016</v>
+        <v>12.4834480767</v>
       </c>
       <c r="P18">
-        <v>61.47432887840001</v>
+        <v>60.9485994333</v>
       </c>
       <c r="Q18">
-        <v>76.87432887840001</v>
+        <v>76.3485994333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09795917772977747</v>
+        <v>0.09849535348769048</v>
       </c>
       <c r="T18">
-        <v>1.204599947569918</v>
+        <v>1.216982759530958</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.30821830641268</v>
+        <v>7.819499582506052</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3330,22 +3330,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08929999339478309</v>
+        <v>0.08932899749655311</v>
       </c>
       <c r="C19">
-        <v>1011.213743121056</v>
+        <v>998.8208394456286</v>
       </c>
       <c r="D19">
-        <v>1020.783883121056</v>
+        <v>1020.230399445629</v>
       </c>
       <c r="E19">
-        <v>201.12814</v>
+        <v>212.96756</v>
       </c>
       <c r="F19">
-        <v>201.27014</v>
+        <v>213.10956</v>
       </c>
       <c r="G19">
         <v>191.7</v>
@@ -3366,45 +3366,45 @@
         <v>84.2</v>
       </c>
       <c r="M19">
-        <v>10.76795249</v>
+        <v>11.571849108</v>
       </c>
       <c r="N19">
-        <v>73.43204751</v>
+        <v>72.62815089200001</v>
       </c>
       <c r="O19">
-        <v>12.4834480767</v>
+        <v>12.34678565164</v>
       </c>
       <c r="P19">
-        <v>60.9485994333</v>
+        <v>60.28136524036</v>
       </c>
       <c r="Q19">
-        <v>76.3485994333</v>
+        <v>75.68136524035999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09849535348769048</v>
+        <v>0.09904460670311356</v>
       </c>
       <c r="T19">
-        <v>1.216982759530958</v>
+        <v>1.229667591295925</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.819499582506052</v>
+        <v>7.276278770502613</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3412,22 +3412,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08932899749655313</v>
+        <v>0.08924512159832314</v>
       </c>
       <c r="C20">
-        <v>998.8208394456284</v>
+        <v>988.5836630543382</v>
       </c>
       <c r="D20">
-        <v>1020.230399445628</v>
+        <v>1021.832643054338</v>
       </c>
       <c r="E20">
-        <v>212.96756</v>
+        <v>224.80698</v>
       </c>
       <c r="F20">
-        <v>213.10956</v>
+        <v>224.94898</v>
       </c>
       <c r="G20">
         <v>191.7</v>
@@ -3448,28 +3448,28 @@
         <v>84.2</v>
       </c>
       <c r="M20">
-        <v>11.571849108</v>
+        <v>12.214729614</v>
       </c>
       <c r="N20">
-        <v>72.62815089200001</v>
+        <v>71.985270386</v>
       </c>
       <c r="O20">
-        <v>12.34678565164</v>
+        <v>12.23749596562</v>
       </c>
       <c r="P20">
-        <v>60.28136524036</v>
+        <v>59.74777442038</v>
       </c>
       <c r="Q20">
-        <v>75.68136524035999</v>
+        <v>75.14777442037999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09904460670311356</v>
+        <v>0.09960742172632486</v>
       </c>
       <c r="T20">
-        <v>1.229667591295925</v>
+        <v>1.242665628783484</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.276278770502613</v>
+        <v>6.893316729949843</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3494,22 +3494,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08924512159832314</v>
+        <v>0.08916124570009316</v>
       </c>
       <c r="C21">
-        <v>988.5836630543382</v>
+        <v>978.351527137468</v>
       </c>
       <c r="D21">
-        <v>1021.832643054338</v>
+        <v>1023.439927137468</v>
       </c>
       <c r="E21">
-        <v>224.80698</v>
+        <v>236.6464</v>
       </c>
       <c r="F21">
-        <v>224.94898</v>
+        <v>236.7884</v>
       </c>
       <c r="G21">
         <v>191.7</v>
@@ -3530,28 +3530,28 @@
         <v>84.2</v>
       </c>
       <c r="M21">
-        <v>12.214729614</v>
+        <v>12.85761012</v>
       </c>
       <c r="N21">
-        <v>71.985270386</v>
+        <v>71.34238988</v>
       </c>
       <c r="O21">
-        <v>12.23749596562</v>
+        <v>12.1282062796</v>
       </c>
       <c r="P21">
-        <v>59.74777442038</v>
+        <v>59.2141836004</v>
       </c>
       <c r="Q21">
-        <v>75.14777442037999</v>
+        <v>74.6141836004</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09960742172632486</v>
+        <v>0.1001843071251164</v>
       </c>
       <c r="T21">
-        <v>1.242665628783484</v>
+        <v>1.255988617208232</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.893316729949843</v>
+        <v>6.548650893452351</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3576,22 +3576,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08916124570009316</v>
+        <v>0.0890773698018632</v>
       </c>
       <c r="C22">
-        <v>978.351527137468</v>
+        <v>968.1244555176203</v>
       </c>
       <c r="D22">
-        <v>1023.439927137468</v>
+        <v>1025.05227551762</v>
       </c>
       <c r="E22">
-        <v>236.6464</v>
+        <v>248.48582</v>
       </c>
       <c r="F22">
-        <v>236.7884</v>
+        <v>248.62782</v>
       </c>
       <c r="G22">
         <v>191.7</v>
@@ -3612,28 +3612,28 @@
         <v>84.2</v>
       </c>
       <c r="M22">
-        <v>12.85761012</v>
+        <v>13.500490626</v>
       </c>
       <c r="N22">
-        <v>71.34238988</v>
+        <v>70.699509374</v>
       </c>
       <c r="O22">
-        <v>12.1282062796</v>
+        <v>12.01891659358</v>
       </c>
       <c r="P22">
-        <v>59.2141836004</v>
+        <v>58.68059278042</v>
       </c>
       <c r="Q22">
-        <v>74.6141836004</v>
+        <v>74.08059278041999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1001843071251164</v>
+        <v>0.1007757972175483</v>
       </c>
       <c r="T22">
-        <v>1.255988617208232</v>
+        <v>1.269648896479176</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.548650893452351</v>
+        <v>6.236810374716526</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3658,22 +3658,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0890773698018632</v>
+        <v>0.08917609390363321</v>
       </c>
       <c r="C23">
-        <v>968.1244555176204</v>
+        <v>954.3877880602524</v>
       </c>
       <c r="D23">
-        <v>1025.05227551762</v>
+        <v>1023.155028060252</v>
       </c>
       <c r="E23">
-        <v>248.48582</v>
+        <v>260.32524</v>
       </c>
       <c r="F23">
-        <v>248.62782</v>
+        <v>260.46724</v>
       </c>
       <c r="G23">
         <v>191.7</v>
@@ -3694,45 +3694,45 @@
         <v>84.2</v>
       </c>
       <c r="M23">
-        <v>13.500490626</v>
+        <v>14.403838372</v>
       </c>
       <c r="N23">
-        <v>70.699509374</v>
+        <v>69.79616162800001</v>
       </c>
       <c r="O23">
-        <v>12.01891659358</v>
+        <v>11.86534747676</v>
       </c>
       <c r="P23">
-        <v>58.68059278042</v>
+        <v>57.93081415124001</v>
       </c>
       <c r="Q23">
-        <v>74.08059278041999</v>
+        <v>73.33081415123999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1007757972175483</v>
+        <v>0.1013824537226067</v>
       </c>
       <c r="T23">
-        <v>1.269648896479176</v>
+        <v>1.28365943932117</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.17</v>
       </c>
       <c r="W23">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.236810374716526</v>
+        <v>5.845664039363188</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3740,22 +3740,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08917609390363321</v>
+        <v>0.08910051800540324</v>
       </c>
       <c r="C24">
-        <v>954.3877880602524</v>
+        <v>944.0001297154049</v>
       </c>
       <c r="D24">
-        <v>1023.155028060252</v>
+        <v>1024.606789715405</v>
       </c>
       <c r="E24">
-        <v>260.32524</v>
+        <v>272.16466</v>
       </c>
       <c r="F24">
-        <v>260.46724</v>
+        <v>272.30666</v>
       </c>
       <c r="G24">
         <v>191.7</v>
@@ -3776,28 +3776,28 @@
         <v>84.2</v>
       </c>
       <c r="M24">
-        <v>14.403838372</v>
+        <v>15.058558298</v>
       </c>
       <c r="N24">
-        <v>69.79616162800001</v>
+        <v>69.14144170200001</v>
       </c>
       <c r="O24">
-        <v>11.86534747676</v>
+        <v>11.75404508934</v>
       </c>
       <c r="P24">
-        <v>57.93081415124001</v>
+        <v>57.38739661266001</v>
       </c>
       <c r="Q24">
-        <v>73.33081415123999</v>
+        <v>72.78739661265999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1013824537226067</v>
+        <v>0.1020048675394847</v>
       </c>
       <c r="T24">
-        <v>1.28365943932117</v>
+        <v>1.298033892366852</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.845664039363188</v>
+        <v>5.591504733303919</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3822,22 +3822,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08910051800540324</v>
+        <v>0.08902494210717324</v>
       </c>
       <c r="C25">
-        <v>944.0001297154049</v>
+        <v>933.6165970535671</v>
       </c>
       <c r="D25">
-        <v>1024.606789715405</v>
+        <v>1026.062677053567</v>
       </c>
       <c r="E25">
-        <v>272.16466</v>
+        <v>284.00408</v>
       </c>
       <c r="F25">
-        <v>272.30666</v>
+        <v>284.14608</v>
       </c>
       <c r="G25">
         <v>191.7</v>
@@ -3858,28 +3858,28 @@
         <v>84.2</v>
       </c>
       <c r="M25">
-        <v>15.058558298</v>
+        <v>15.713278224</v>
       </c>
       <c r="N25">
-        <v>69.14144170200001</v>
+        <v>68.486721776</v>
       </c>
       <c r="O25">
-        <v>11.75404508934</v>
+        <v>11.64274270192</v>
       </c>
       <c r="P25">
-        <v>57.38739661266001</v>
+        <v>56.84397907408</v>
       </c>
       <c r="Q25">
-        <v>72.78739661265999</v>
+        <v>72.24397907407999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020048675394847</v>
+        <v>0.1026436606673332</v>
       </c>
       <c r="T25">
-        <v>1.298033892366852</v>
+        <v>1.312786620492684</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.591504733303919</v>
+        <v>5.358525369416254</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3904,22 +3904,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08902494210717324</v>
+        <v>0.08894936620894328</v>
       </c>
       <c r="C26">
-        <v>933.6165970535671</v>
+        <v>923.2372076865963</v>
       </c>
       <c r="D26">
-        <v>1026.062677053567</v>
+        <v>1027.522707686596</v>
       </c>
       <c r="E26">
-        <v>284.00408</v>
+        <v>295.8435</v>
       </c>
       <c r="F26">
-        <v>284.14608</v>
+        <v>295.9855</v>
       </c>
       <c r="G26">
         <v>191.7</v>
@@ -3940,28 +3940,28 @@
         <v>84.2</v>
       </c>
       <c r="M26">
-        <v>15.713278224</v>
+        <v>16.36799815</v>
       </c>
       <c r="N26">
-        <v>68.486721776</v>
+        <v>67.83200185</v>
       </c>
       <c r="O26">
-        <v>11.64274270192</v>
+        <v>11.5314403145</v>
       </c>
       <c r="P26">
-        <v>56.84397907408</v>
+        <v>56.30056153549999</v>
       </c>
       <c r="Q26">
-        <v>72.24397907407999</v>
+        <v>71.70056153549999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1026436606673332</v>
+        <v>0.103299488278591</v>
       </c>
       <c r="T26">
-        <v>1.312786620492684</v>
+        <v>1.327932754701871</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.358525369416255</v>
+        <v>5.144184354639605</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3986,22 +3986,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08894936620894328</v>
+        <v>0.0888737903107133</v>
       </c>
       <c r="C27">
-        <v>923.2372076865963</v>
+        <v>912.861979326738</v>
       </c>
       <c r="D27">
-        <v>1027.522707686596</v>
+        <v>1028.986899326738</v>
       </c>
       <c r="E27">
-        <v>295.8435</v>
+        <v>307.68292</v>
       </c>
       <c r="F27">
-        <v>295.9855</v>
+        <v>307.82492</v>
       </c>
       <c r="G27">
         <v>191.7</v>
@@ -4022,28 +4022,28 @@
         <v>84.2</v>
       </c>
       <c r="M27">
-        <v>16.36799815</v>
+        <v>17.022718076</v>
       </c>
       <c r="N27">
-        <v>67.83200185</v>
+        <v>67.177281924</v>
       </c>
       <c r="O27">
-        <v>11.5314403145</v>
+        <v>11.42013792708</v>
       </c>
       <c r="P27">
-        <v>56.30056153549999</v>
+        <v>55.75714399692</v>
       </c>
       <c r="Q27">
-        <v>71.70056153549999</v>
+        <v>71.15714399691998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.103299488278591</v>
+        <v>0.1039730409604234</v>
       </c>
       <c r="T27">
-        <v>1.327932754701871</v>
+        <v>1.343488243889685</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.144184354639605</v>
+        <v>4.946331110230389</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4068,22 +4068,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0888737903107133</v>
+        <v>0.08879821441248331</v>
       </c>
       <c r="C28">
-        <v>912.861979326738</v>
+        <v>902.490929787338</v>
       </c>
       <c r="D28">
-        <v>1028.986899326738</v>
+        <v>1030.455269787338</v>
       </c>
       <c r="E28">
-        <v>307.68292</v>
+        <v>319.52234</v>
       </c>
       <c r="F28">
-        <v>307.82492</v>
+        <v>319.66434</v>
       </c>
       <c r="G28">
         <v>191.7</v>
@@ -4104,28 +4104,28 @@
         <v>84.2</v>
       </c>
       <c r="M28">
-        <v>17.022718076</v>
+        <v>17.677438002</v>
       </c>
       <c r="N28">
-        <v>67.177281924</v>
+        <v>66.522561998</v>
       </c>
       <c r="O28">
-        <v>11.42013792708</v>
+        <v>11.30883553966</v>
       </c>
       <c r="P28">
-        <v>55.75714399692</v>
+        <v>55.21372645834</v>
       </c>
       <c r="Q28">
-        <v>71.15714399691998</v>
+        <v>70.61372645833998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1039730409604234</v>
+        <v>0.1046650471403881</v>
       </c>
       <c r="T28">
-        <v>1.343488243889685</v>
+        <v>1.359469910863466</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.946331110230389</v>
+        <v>4.763133661703337</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4150,22 +4150,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08879821441248331</v>
+        <v>0.08872263851425333</v>
       </c>
       <c r="C29">
-        <v>902.490929787338</v>
+        <v>892.1240769835665</v>
       </c>
       <c r="D29">
-        <v>1030.455269787338</v>
+        <v>1031.927836983567</v>
       </c>
       <c r="E29">
-        <v>319.52234</v>
+        <v>331.3617600000001</v>
       </c>
       <c r="F29">
-        <v>319.66434</v>
+        <v>331.5037600000001</v>
       </c>
       <c r="G29">
         <v>191.7</v>
@@ -4186,28 +4186,28 @@
         <v>84.2</v>
       </c>
       <c r="M29">
-        <v>17.677438002</v>
+        <v>18.332157928</v>
       </c>
       <c r="N29">
-        <v>66.522561998</v>
+        <v>65.867842072</v>
       </c>
       <c r="O29">
-        <v>11.30883553966</v>
+        <v>11.19753315224</v>
       </c>
       <c r="P29">
-        <v>55.21372645834</v>
+        <v>54.67030891976</v>
       </c>
       <c r="Q29">
-        <v>70.61372645833998</v>
+        <v>70.07030891976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1046650471403881</v>
+        <v>0.1053762757142407</v>
       </c>
       <c r="T29">
-        <v>1.359469910863466</v>
+        <v>1.375895513030964</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.763133661703337</v>
+        <v>4.593021745213932</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4232,22 +4232,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08872263851425333</v>
+        <v>0.08924881261602337</v>
       </c>
       <c r="C30">
-        <v>892.1240769835665</v>
+        <v>870.1188493505954</v>
       </c>
       <c r="D30">
-        <v>1031.927836983567</v>
+        <v>1021.762029350595</v>
       </c>
       <c r="E30">
-        <v>331.3617600000001</v>
+        <v>343.20118</v>
       </c>
       <c r="F30">
-        <v>331.5037600000001</v>
+        <v>343.34318</v>
       </c>
       <c r="G30">
         <v>191.7</v>
@@ -4268,45 +4268,45 @@
         <v>84.2</v>
       </c>
       <c r="M30">
-        <v>18.332157928</v>
+        <v>19.845235804</v>
       </c>
       <c r="N30">
-        <v>65.867842072</v>
+        <v>64.354764196</v>
       </c>
       <c r="O30">
-        <v>11.19753315224</v>
+        <v>10.94030991332</v>
       </c>
       <c r="P30">
-        <v>54.67030891976</v>
+        <v>53.41445428268</v>
       </c>
       <c r="Q30">
-        <v>70.07030891976</v>
+        <v>68.81445428268</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1053762757142407</v>
+        <v>0.1061075388958076</v>
       </c>
       <c r="T30">
-        <v>1.375895513030964</v>
+        <v>1.392783808217265</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.17</v>
       </c>
       <c r="W30">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.593021745213932</v>
+        <v>4.242831923570728</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08924881261602337</v>
+        <v>0.08919398671779338</v>
       </c>
       <c r="C31">
-        <v>870.1188493505955</v>
+        <v>859.3293213538574</v>
       </c>
       <c r="D31">
-        <v>1021.762029350595</v>
+        <v>1022.811921353857</v>
       </c>
       <c r="E31">
-        <v>343.20118</v>
+        <v>355.0406</v>
       </c>
       <c r="F31">
-        <v>343.34318</v>
+        <v>355.1826</v>
       </c>
       <c r="G31">
         <v>191.7</v>
@@ -4350,28 +4350,28 @@
         <v>84.2</v>
       </c>
       <c r="M31">
-        <v>19.845235804</v>
+        <v>20.52955428</v>
       </c>
       <c r="N31">
-        <v>64.354764196</v>
+        <v>63.67044572</v>
       </c>
       <c r="O31">
-        <v>10.94030991332</v>
+        <v>10.8239757724</v>
       </c>
       <c r="P31">
-        <v>53.41445428268</v>
+        <v>52.8464699476</v>
       </c>
       <c r="Q31">
-        <v>68.81445428268</v>
+        <v>68.24646994759999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1061075388958076</v>
+        <v>0.1068596953111334</v>
       </c>
       <c r="T31">
-        <v>1.392783808217264</v>
+        <v>1.410154626123173</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.242831923570728</v>
+        <v>4.101404192785037</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4396,22 +4396,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08919398671779338</v>
+        <v>0.0900397108195634</v>
       </c>
       <c r="C32">
-        <v>859.3293213538574</v>
+        <v>831.5309671881256</v>
       </c>
       <c r="D32">
-        <v>1022.811921353857</v>
+        <v>1006.852987188126</v>
       </c>
       <c r="E32">
-        <v>355.0406</v>
+        <v>366.88002</v>
       </c>
       <c r="F32">
-        <v>355.1826</v>
+        <v>367.02202</v>
       </c>
       <c r="G32">
         <v>191.7</v>
@@ -4432,45 +4432,45 @@
         <v>84.2</v>
       </c>
       <c r="M32">
-        <v>20.52955428</v>
+        <v>22.498449826</v>
       </c>
       <c r="N32">
-        <v>63.67044572</v>
+        <v>61.701550174</v>
       </c>
       <c r="O32">
-        <v>10.8239757724</v>
+        <v>10.48926352958</v>
       </c>
       <c r="P32">
-        <v>52.8464699476</v>
+        <v>51.21228664442</v>
       </c>
       <c r="Q32">
-        <v>68.24646994759999</v>
+        <v>66.61228664442</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1068596953111334</v>
+        <v>0.1076336533616861</v>
       </c>
       <c r="T32">
-        <v>1.410154626123173</v>
+        <v>1.428028945997369</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.17</v>
       </c>
       <c r="W32">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.101404192785037</v>
+        <v>3.742480066457535</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4478,22 +4478,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0900397108195634</v>
+        <v>0.09001393492133342</v>
       </c>
       <c r="C33">
-        <v>831.5309671881256</v>
+        <v>820.1705806399904</v>
       </c>
       <c r="D33">
-        <v>1006.852987188126</v>
+        <v>1007.33202063999</v>
       </c>
       <c r="E33">
-        <v>366.88002</v>
+        <v>378.71944</v>
       </c>
       <c r="F33">
-        <v>367.02202</v>
+        <v>378.86144</v>
       </c>
       <c r="G33">
         <v>191.7</v>
@@ -4514,28 +4514,28 @@
         <v>84.2</v>
       </c>
       <c r="M33">
-        <v>22.498449826</v>
+        <v>23.224206272</v>
       </c>
       <c r="N33">
-        <v>61.701550174</v>
+        <v>60.975793728</v>
       </c>
       <c r="O33">
-        <v>10.48926352958</v>
+        <v>10.36588493376</v>
       </c>
       <c r="P33">
-        <v>51.21228664442</v>
+        <v>50.60990879424</v>
       </c>
       <c r="Q33">
-        <v>66.61228664442</v>
+        <v>66.00990879423999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1076336533616861</v>
+        <v>0.1084303748843139</v>
       </c>
       <c r="T33">
-        <v>1.428028945997369</v>
+        <v>1.446428981161983</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.742480066457535</v>
+        <v>3.625527564380737</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4560,22 +4560,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09001393492133342</v>
+        <v>0.08998815902310346</v>
       </c>
       <c r="C34">
-        <v>820.1705806399904</v>
+        <v>808.8106501311773</v>
       </c>
       <c r="D34">
-        <v>1007.33202063999</v>
+        <v>1007.811510131177</v>
       </c>
       <c r="E34">
-        <v>378.71944</v>
+        <v>390.55886</v>
       </c>
       <c r="F34">
-        <v>378.86144</v>
+        <v>390.70086</v>
       </c>
       <c r="G34">
         <v>191.7</v>
@@ -4596,28 +4596,28 @@
         <v>84.2</v>
       </c>
       <c r="M34">
-        <v>23.224206272</v>
+        <v>23.949962718</v>
       </c>
       <c r="N34">
-        <v>60.975793728</v>
+        <v>60.250037282</v>
       </c>
       <c r="O34">
-        <v>10.36588493376</v>
+        <v>10.24250633794</v>
       </c>
       <c r="P34">
-        <v>50.60990879424</v>
+        <v>50.00753094406</v>
       </c>
       <c r="Q34">
-        <v>66.00990879423999</v>
+        <v>65.40753094406</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1084303748843139</v>
+        <v>0.1092508791389604</v>
       </c>
       <c r="T34">
-        <v>1.446428981161983</v>
+        <v>1.46537827110763</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.625527564380737</v>
+        <v>3.515663092732836</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4642,22 +4642,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08998815902310346</v>
+        <v>0.09075254312487346</v>
       </c>
       <c r="C35">
-        <v>808.8106501311773</v>
+        <v>782.9432199288063</v>
       </c>
       <c r="D35">
-        <v>1007.811510131177</v>
+        <v>993.7834999288065</v>
       </c>
       <c r="E35">
-        <v>390.55886</v>
+        <v>402.3982800000001</v>
       </c>
       <c r="F35">
-        <v>390.70086</v>
+        <v>402.5402800000001</v>
       </c>
       <c r="G35">
         <v>191.7</v>
@@ -4678,45 +4678,45 @@
         <v>84.2</v>
       </c>
       <c r="M35">
-        <v>23.949962718</v>
+        <v>25.80283194800001</v>
       </c>
       <c r="N35">
-        <v>60.250037282</v>
+        <v>58.397168052</v>
       </c>
       <c r="O35">
-        <v>10.24250633794</v>
+        <v>9.92751856884</v>
       </c>
       <c r="P35">
-        <v>50.00753094406</v>
+        <v>48.46964948316</v>
       </c>
       <c r="Q35">
-        <v>65.40753094406</v>
+        <v>63.86964948315999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1092508791389604</v>
+        <v>0.1100962471588992</v>
       </c>
       <c r="T35">
-        <v>1.46537827110763</v>
+        <v>1.484901781960721</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.17</v>
       </c>
       <c r="W35">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.515663092732836</v>
+        <v>3.263207704087939</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4724,22 +4724,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09075254312487346</v>
+        <v>0.09075000722664348</v>
       </c>
       <c r="C36">
-        <v>782.9432199288063</v>
+        <v>771.1496931742618</v>
       </c>
       <c r="D36">
-        <v>993.7834999288065</v>
+        <v>993.8293931742617</v>
       </c>
       <c r="E36">
-        <v>402.3982800000001</v>
+        <v>414.2377</v>
       </c>
       <c r="F36">
-        <v>402.5402800000001</v>
+        <v>414.3797</v>
       </c>
       <c r="G36">
         <v>191.7</v>
@@ -4760,28 +4760,28 @@
         <v>84.2</v>
       </c>
       <c r="M36">
-        <v>25.80283194800001</v>
+        <v>26.56173877</v>
       </c>
       <c r="N36">
-        <v>58.397168052</v>
+        <v>57.63826123</v>
       </c>
       <c r="O36">
-        <v>9.92751856884</v>
+        <v>9.7985044091</v>
       </c>
       <c r="P36">
-        <v>48.46964948316</v>
+        <v>47.8397568209</v>
       </c>
       <c r="Q36">
-        <v>63.86964948315999</v>
+        <v>63.23975682089999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1100962471588992</v>
+        <v>0.1109676265025284</v>
       </c>
       <c r="T36">
-        <v>1.484901781960721</v>
+        <v>1.505026016224676</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.263207704087939</v>
+        <v>3.169973198256855</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4806,22 +4806,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09075000722664348</v>
+        <v>0.09074747132841351</v>
       </c>
       <c r="C37">
-        <v>771.1496931742618</v>
+        <v>759.3561706586422</v>
       </c>
       <c r="D37">
-        <v>993.8293931742617</v>
+        <v>993.8752906586421</v>
       </c>
       <c r="E37">
-        <v>414.2377</v>
+        <v>426.07712</v>
       </c>
       <c r="F37">
-        <v>414.3797</v>
+        <v>426.21912</v>
       </c>
       <c r="G37">
         <v>191.7</v>
@@ -4842,28 +4842,28 @@
         <v>84.2</v>
       </c>
       <c r="M37">
-        <v>26.56173877</v>
+        <v>27.32064559200001</v>
       </c>
       <c r="N37">
-        <v>57.63826123</v>
+        <v>56.879354408</v>
       </c>
       <c r="O37">
-        <v>9.7985044091</v>
+        <v>9.669490249360001</v>
       </c>
       <c r="P37">
-        <v>47.8397568209</v>
+        <v>47.20986415863999</v>
       </c>
       <c r="Q37">
-        <v>63.23975682089999</v>
+        <v>62.60986415863999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1109676265025284</v>
+        <v>0.1118662364506461</v>
       </c>
       <c r="T37">
-        <v>1.505026016224676</v>
+        <v>1.525779132809379</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.169973198256855</v>
+        <v>3.081918387194164</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4888,22 +4888,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09074747132841351</v>
+        <v>0.09314031543018356</v>
       </c>
       <c r="C38">
-        <v>759.3561706586422</v>
+        <v>706.0149511553864</v>
       </c>
       <c r="D38">
-        <v>993.8752906586421</v>
+        <v>952.3734911553864</v>
       </c>
       <c r="E38">
-        <v>426.07712</v>
+        <v>437.91654</v>
       </c>
       <c r="F38">
-        <v>426.21912</v>
+        <v>438.05854</v>
       </c>
       <c r="G38">
         <v>191.7</v>
@@ -4924,45 +4924,45 @@
         <v>84.2</v>
       </c>
       <c r="M38">
-        <v>27.320645592</v>
+        <v>31.496409026</v>
       </c>
       <c r="N38">
-        <v>56.879354408</v>
+        <v>52.703590974</v>
       </c>
       <c r="O38">
-        <v>9.669490249360001</v>
+        <v>8.959610465580001</v>
       </c>
       <c r="P38">
-        <v>47.20986415863999</v>
+        <v>43.74398050842</v>
       </c>
       <c r="Q38">
-        <v>62.60986415863999</v>
+        <v>59.14398050841999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1118662364506461</v>
+        <v>0.112793373698704</v>
       </c>
       <c r="T38">
-        <v>1.525779132809379</v>
+        <v>1.54719107849201</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.17</v>
       </c>
       <c r="W38">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.081918387194164</v>
+        <v>2.67332062936107</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4970,22 +4970,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09314031543018356</v>
+        <v>0.09320251953195356</v>
       </c>
       <c r="C39">
-        <v>706.0149511553864</v>
+        <v>693.1428273670267</v>
       </c>
       <c r="D39">
-        <v>952.3734911553864</v>
+        <v>951.3407873670268</v>
       </c>
       <c r="E39">
-        <v>437.91654</v>
+        <v>449.75596</v>
       </c>
       <c r="F39">
-        <v>438.05854</v>
+        <v>449.89796</v>
       </c>
       <c r="G39">
         <v>191.7</v>
@@ -5006,28 +5006,28 @@
         <v>84.2</v>
       </c>
       <c r="M39">
-        <v>31.496409026</v>
+        <v>32.347663324</v>
       </c>
       <c r="N39">
-        <v>52.703590974</v>
+        <v>51.852336676</v>
       </c>
       <c r="O39">
-        <v>8.959610465580001</v>
+        <v>8.81489723492</v>
       </c>
       <c r="P39">
-        <v>43.74398050842</v>
+        <v>43.03743944108</v>
       </c>
       <c r="Q39">
-        <v>59.14398050841999</v>
+        <v>58.43743944107999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.112793373698704</v>
+        <v>0.1137504185999251</v>
       </c>
       <c r="T39">
-        <v>1.54719107849201</v>
+        <v>1.569293732099887</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.67332062936107</v>
+        <v>2.602970086483147</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5052,22 +5052,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09320251953195356</v>
+        <v>0.09326472363372358</v>
       </c>
       <c r="C40">
-        <v>693.1428273670267</v>
+        <v>680.2729407722582</v>
       </c>
       <c r="D40">
-        <v>951.3407873670268</v>
+        <v>950.3103207722581</v>
       </c>
       <c r="E40">
-        <v>449.75596</v>
+        <v>461.59538</v>
       </c>
       <c r="F40">
-        <v>449.89796</v>
+        <v>461.73738</v>
       </c>
       <c r="G40">
         <v>191.7</v>
@@ -5088,28 +5088,28 @@
         <v>84.2</v>
       </c>
       <c r="M40">
-        <v>32.347663324</v>
+        <v>33.198917622</v>
       </c>
       <c r="N40">
-        <v>51.852336676</v>
+        <v>51.001082378</v>
       </c>
       <c r="O40">
-        <v>8.81489723492</v>
+        <v>8.670184004260001</v>
       </c>
       <c r="P40">
-        <v>43.03743944108</v>
+        <v>42.33089837374</v>
       </c>
       <c r="Q40">
-        <v>58.43743944107999</v>
+        <v>57.73089837373999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1137504185999251</v>
+        <v>0.1147388420224977</v>
       </c>
       <c r="T40">
-        <v>1.569293732099887</v>
+        <v>1.592121062875235</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.602970086483147</v>
+        <v>2.53622726375281</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5134,22 +5134,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09326472363372358</v>
+        <v>0.09462172773549361</v>
       </c>
       <c r="C41">
-        <v>680.2729407722582</v>
+        <v>646.4962565753804</v>
       </c>
       <c r="D41">
-        <v>950.3103207722581</v>
+        <v>928.3730565753804</v>
       </c>
       <c r="E41">
-        <v>461.59538</v>
+        <v>473.4348000000001</v>
       </c>
       <c r="F41">
-        <v>461.73738</v>
+        <v>473.5768</v>
       </c>
       <c r="G41">
         <v>191.7</v>
@@ -5170,45 +5170,45 @@
         <v>84.2</v>
       </c>
       <c r="M41">
-        <v>33.198917622</v>
+        <v>35.89712144000001</v>
       </c>
       <c r="N41">
-        <v>51.001082378</v>
+        <v>48.30287856</v>
       </c>
       <c r="O41">
-        <v>8.670184004260001</v>
+        <v>8.211489355199999</v>
       </c>
       <c r="P41">
-        <v>42.33089837374</v>
+        <v>40.0913892048</v>
       </c>
       <c r="Q41">
-        <v>57.73089837373999</v>
+        <v>55.49138920479999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1147388420224977</v>
+        <v>0.1157602128924894</v>
       </c>
       <c r="T41">
-        <v>1.592121062875235</v>
+        <v>1.615709304676428</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.17</v>
       </c>
       <c r="W41">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.53622726375281</v>
+        <v>2.345591975689068</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5216,22 +5216,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09462172773549361</v>
+        <v>0.09471630183726364</v>
       </c>
       <c r="C42">
-        <v>646.4962565753804</v>
+        <v>633.1656483317247</v>
       </c>
       <c r="D42">
-        <v>928.3730565753804</v>
+        <v>926.8818683317248</v>
       </c>
       <c r="E42">
-        <v>473.4348000000001</v>
+        <v>485.2742200000001</v>
       </c>
       <c r="F42">
-        <v>473.5768</v>
+        <v>485.4162200000001</v>
       </c>
       <c r="G42">
         <v>191.7</v>
@@ -5252,28 +5252,28 @@
         <v>84.2</v>
       </c>
       <c r="M42">
-        <v>35.89712144000001</v>
+        <v>36.79454947600001</v>
       </c>
       <c r="N42">
-        <v>48.30287856</v>
+        <v>47.405450524</v>
       </c>
       <c r="O42">
-        <v>8.211489355199999</v>
+        <v>8.05892658908</v>
       </c>
       <c r="P42">
-        <v>40.0913892048</v>
+        <v>39.34652393491999</v>
       </c>
       <c r="Q42">
-        <v>55.49138920479999</v>
+        <v>54.74652393491998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1157602128924894</v>
+        <v>0.1168162065038367</v>
       </c>
       <c r="T42">
-        <v>1.615709304676428</v>
+        <v>1.640097147894611</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.345591975689068</v>
+        <v>2.288382415306407</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5298,22 +5298,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09471630183726364</v>
+        <v>0.09481087593903365</v>
       </c>
       <c r="C43">
-        <v>633.1656483317247</v>
+        <v>619.8398228128392</v>
       </c>
       <c r="D43">
-        <v>926.8818683317248</v>
+        <v>925.3954628128392</v>
       </c>
       <c r="E43">
-        <v>485.2742200000001</v>
+        <v>497.11364</v>
       </c>
       <c r="F43">
-        <v>485.4162200000001</v>
+        <v>497.25564</v>
       </c>
       <c r="G43">
         <v>191.7</v>
@@ -5334,28 +5334,28 @@
         <v>84.2</v>
       </c>
       <c r="M43">
-        <v>36.79454947600001</v>
+        <v>37.69197751200001</v>
       </c>
       <c r="N43">
-        <v>47.405450524</v>
+        <v>46.50802248799999</v>
       </c>
       <c r="O43">
-        <v>8.05892658908</v>
+        <v>7.90636382296</v>
       </c>
       <c r="P43">
-        <v>39.34652393491999</v>
+        <v>38.60165866503999</v>
       </c>
       <c r="Q43">
-        <v>54.74652393491998</v>
+        <v>54.00165866503998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1168162065038367</v>
+        <v>0.1179086136879891</v>
       </c>
       <c r="T43">
-        <v>1.640097147894611</v>
+        <v>1.665325951223766</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.288382415306407</v>
+        <v>2.233897119703874</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5380,22 +5380,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09481087593903366</v>
+        <v>0.09490545004080368</v>
       </c>
       <c r="C44">
-        <v>619.8398228128391</v>
+        <v>606.5187570459369</v>
       </c>
       <c r="D44">
-        <v>925.395462812839</v>
+        <v>923.9138170459369</v>
       </c>
       <c r="E44">
-        <v>497.11364</v>
+        <v>508.95306</v>
       </c>
       <c r="F44">
-        <v>497.25564</v>
+        <v>509.09506</v>
       </c>
       <c r="G44">
         <v>191.7</v>
@@ -5416,28 +5416,28 @@
         <v>84.2</v>
       </c>
       <c r="M44">
-        <v>37.691977512</v>
+        <v>38.589405548</v>
       </c>
       <c r="N44">
-        <v>46.508022488</v>
+        <v>45.610594452</v>
       </c>
       <c r="O44">
-        <v>7.906363822960001</v>
+        <v>7.75380105684</v>
       </c>
       <c r="P44">
-        <v>38.60165866504</v>
+        <v>37.85679339516</v>
       </c>
       <c r="Q44">
-        <v>54.00165866503999</v>
+        <v>53.25679339515999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1179086136879891</v>
+        <v>0.1190393509487784</v>
       </c>
       <c r="T44">
-        <v>1.665325951223765</v>
+        <v>1.691439975722364</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.233897119703874</v>
+        <v>2.181946023896807</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09490545004080368</v>
+        <v>0.09500002414257371</v>
       </c>
       <c r="C45">
-        <v>606.5187570459369</v>
+        <v>593.2024282051237</v>
       </c>
       <c r="D45">
-        <v>923.9138170459369</v>
+        <v>922.4369082051238</v>
       </c>
       <c r="E45">
-        <v>508.95306</v>
+        <v>520.79248</v>
       </c>
       <c r="F45">
-        <v>509.09506</v>
+        <v>520.93448</v>
       </c>
       <c r="G45">
         <v>191.7</v>
@@ -5498,28 +5498,28 @@
         <v>84.2</v>
       </c>
       <c r="M45">
-        <v>38.589405548</v>
+        <v>39.486833584</v>
       </c>
       <c r="N45">
-        <v>45.610594452</v>
+        <v>44.713166416</v>
       </c>
       <c r="O45">
-        <v>7.75380105684</v>
+        <v>7.60123829072</v>
       </c>
       <c r="P45">
-        <v>37.85679339516</v>
+        <v>37.11192812528</v>
       </c>
       <c r="Q45">
-        <v>53.25679339515999</v>
+        <v>52.51192812527999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1190393509487784</v>
+        <v>0.1202104716831673</v>
       </c>
       <c r="T45">
-        <v>1.691439975722364</v>
+        <v>1.718486643953056</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.181946023896807</v>
+        <v>2.132356341535516</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5544,22 +5544,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09500002414257371</v>
+        <v>0.09509459824434371</v>
       </c>
       <c r="C46">
-        <v>593.2024282051237</v>
+        <v>579.8908136102249</v>
       </c>
       <c r="D46">
-        <v>922.4369082051238</v>
+        <v>920.964713610225</v>
       </c>
       <c r="E46">
-        <v>520.79248</v>
+        <v>532.6319</v>
       </c>
       <c r="F46">
-        <v>520.93448</v>
+        <v>532.7739</v>
       </c>
       <c r="G46">
         <v>191.7</v>
@@ -5580,28 +5580,28 @@
         <v>84.2</v>
       </c>
       <c r="M46">
-        <v>39.486833584</v>
+        <v>40.38426162</v>
       </c>
       <c r="N46">
-        <v>44.713166416</v>
+        <v>43.81573838</v>
       </c>
       <c r="O46">
-        <v>7.60123829072</v>
+        <v>7.4486755246</v>
       </c>
       <c r="P46">
-        <v>37.11192812528</v>
+        <v>36.3670628554</v>
       </c>
       <c r="Q46">
-        <v>52.51192812527999</v>
+        <v>51.76706285539999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1202104716831673</v>
+        <v>0.1214241786260795</v>
       </c>
       <c r="T46">
-        <v>1.718486643953056</v>
+        <v>1.746516827392136</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.132356341535516</v>
+        <v>2.084970645056949</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5626,22 +5626,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09509459824434371</v>
+        <v>0.09518917234611374</v>
       </c>
       <c r="C47">
-        <v>579.8908136102249</v>
+        <v>566.5838907256222</v>
       </c>
       <c r="D47">
-        <v>920.964713610225</v>
+        <v>919.4972107256222</v>
       </c>
       <c r="E47">
-        <v>532.6319</v>
+        <v>544.47132</v>
       </c>
       <c r="F47">
-        <v>532.7739</v>
+        <v>544.61332</v>
       </c>
       <c r="G47">
         <v>191.7</v>
@@ -5662,28 +5662,28 @@
         <v>84.2</v>
       </c>
       <c r="M47">
-        <v>40.38426162</v>
+        <v>41.281689656</v>
       </c>
       <c r="N47">
-        <v>43.81573838</v>
+        <v>42.918310344</v>
       </c>
       <c r="O47">
-        <v>7.4486755246</v>
+        <v>7.296112758480001</v>
       </c>
       <c r="P47">
-        <v>36.3670628554</v>
+        <v>35.62219758552</v>
       </c>
       <c r="Q47">
-        <v>51.76706285539999</v>
+        <v>51.02219758551999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1214241786260795</v>
+        <v>0.1226828376779884</v>
       </c>
       <c r="T47">
-        <v>1.746516827392136</v>
+        <v>1.775585165773404</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.084970645056949</v>
+        <v>2.039645196251363</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5708,22 +5708,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09518917234611374</v>
+        <v>0.1008231664478837</v>
       </c>
       <c r="C48">
-        <v>566.5838907256222</v>
+        <v>475.0283381764915</v>
       </c>
       <c r="D48">
-        <v>919.4972107256222</v>
+        <v>839.7810781764916</v>
       </c>
       <c r="E48">
-        <v>544.47132</v>
+        <v>556.31074</v>
       </c>
       <c r="F48">
-        <v>544.61332</v>
+        <v>556.4527400000001</v>
       </c>
       <c r="G48">
         <v>191.7</v>
@@ -5744,45 +5744,45 @@
         <v>84.2</v>
       </c>
       <c r="M48">
-        <v>41.281689656</v>
+        <v>50.0807466</v>
       </c>
       <c r="N48">
-        <v>42.918310344</v>
+        <v>34.1192534</v>
       </c>
       <c r="O48">
-        <v>7.296112758480001</v>
+        <v>5.800273078</v>
       </c>
       <c r="P48">
-        <v>35.62219758552</v>
+        <v>28.318980322</v>
       </c>
       <c r="Q48">
-        <v>51.02219758551999</v>
+        <v>43.71898032199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1226828376779884</v>
+        <v>0.1239889932978939</v>
       </c>
       <c r="T48">
-        <v>1.775585165773404</v>
+        <v>1.805750422584155</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.17</v>
       </c>
       <c r="W48">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.039645196251363</v>
+        <v>1.68128483931188</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5790,22 +5790,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1008231664478837</v>
+        <v>0.1010356005496538</v>
       </c>
       <c r="C49">
-        <v>475.0283381764915</v>
+        <v>460.4526895656974</v>
       </c>
       <c r="D49">
-        <v>839.7810781764916</v>
+        <v>837.0448495656974</v>
       </c>
       <c r="E49">
-        <v>556.31074</v>
+        <v>568.15016</v>
       </c>
       <c r="F49">
-        <v>556.4527400000001</v>
+        <v>568.2921600000001</v>
       </c>
       <c r="G49">
         <v>191.7</v>
@@ -5826,28 +5826,28 @@
         <v>84.2</v>
       </c>
       <c r="M49">
-        <v>50.0807466</v>
+        <v>51.1462944</v>
       </c>
       <c r="N49">
-        <v>34.1192534</v>
+        <v>33.0537056</v>
       </c>
       <c r="O49">
-        <v>5.800273078</v>
+        <v>5.619129952000001</v>
       </c>
       <c r="P49">
-        <v>28.318980322</v>
+        <v>27.434575648</v>
       </c>
       <c r="Q49">
-        <v>43.71898032199999</v>
+        <v>42.83457564799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1239889932978939</v>
+        <v>0.1253453856724111</v>
       </c>
       <c r="T49">
-        <v>1.805750422584155</v>
+        <v>1.837075881579934</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.68128483931188</v>
+        <v>1.646258071826216</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5872,22 +5872,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1010356005496538</v>
+        <v>0.1012480346514238</v>
       </c>
       <c r="C50">
-        <v>460.4526895656977</v>
+        <v>445.8948137577888</v>
       </c>
       <c r="D50">
-        <v>837.0448495656976</v>
+        <v>834.3263937577888</v>
       </c>
       <c r="E50">
-        <v>568.1501599999999</v>
+        <v>579.9895799999999</v>
       </c>
       <c r="F50">
-        <v>568.29216</v>
+        <v>580.13158</v>
       </c>
       <c r="G50">
         <v>191.7</v>
@@ -5908,28 +5908,28 @@
         <v>84.2</v>
       </c>
       <c r="M50">
-        <v>51.1462944</v>
+        <v>52.2118422</v>
       </c>
       <c r="N50">
-        <v>33.05370560000001</v>
+        <v>31.9881578</v>
       </c>
       <c r="O50">
-        <v>5.619129952000002</v>
+        <v>5.437986826000001</v>
       </c>
       <c r="P50">
-        <v>27.43457564800001</v>
+        <v>26.550170974</v>
       </c>
       <c r="Q50">
-        <v>42.834575648</v>
+        <v>41.950170974</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1253453856724111</v>
+        <v>0.1267549699047526</v>
       </c>
       <c r="T50">
-        <v>1.837075881579934</v>
+        <v>1.869629789948096</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.646258071826217</v>
+        <v>1.612660968319559</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5954,22 +5954,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1012480346514238</v>
+        <v>0.1014604687531938</v>
       </c>
       <c r="C51">
-        <v>445.8948137577888</v>
+        <v>431.3545381520614</v>
       </c>
       <c r="D51">
-        <v>834.3263937577888</v>
+        <v>831.6255381520615</v>
       </c>
       <c r="E51">
-        <v>579.9895799999999</v>
+        <v>591.829</v>
       </c>
       <c r="F51">
-        <v>580.13158</v>
+        <v>591.971</v>
       </c>
       <c r="G51">
         <v>191.7</v>
@@ -5990,28 +5990,28 @@
         <v>84.2</v>
       </c>
       <c r="M51">
-        <v>52.2118422</v>
+        <v>53.27739</v>
       </c>
       <c r="N51">
-        <v>31.9881578</v>
+        <v>30.92261000000001</v>
       </c>
       <c r="O51">
-        <v>5.437986826000001</v>
+        <v>5.256843700000001</v>
       </c>
       <c r="P51">
-        <v>26.550170974</v>
+        <v>25.6657663</v>
       </c>
       <c r="Q51">
-        <v>41.950170974</v>
+        <v>41.06576629999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1267549699047526</v>
+        <v>0.1282209375063877</v>
       </c>
       <c r="T51">
-        <v>1.869629789948096</v>
+        <v>1.903485854650985</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.612660968319559</v>
+        <v>1.580407748953168</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6036,22 +6036,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1014604687531938</v>
+        <v>0.1016729028549638</v>
       </c>
       <c r="C52">
-        <v>431.3545381520614</v>
+        <v>416.8316923755506</v>
       </c>
       <c r="D52">
-        <v>831.6255381520615</v>
+        <v>828.9421123755507</v>
       </c>
       <c r="E52">
-        <v>591.829</v>
+        <v>603.66842</v>
       </c>
       <c r="F52">
-        <v>591.971</v>
+        <v>603.81042</v>
       </c>
       <c r="G52">
         <v>191.7</v>
@@ -6072,28 +6072,28 @@
         <v>84.2</v>
       </c>
       <c r="M52">
-        <v>53.27739</v>
+        <v>54.3429378</v>
       </c>
       <c r="N52">
-        <v>30.92261000000001</v>
+        <v>29.8570622</v>
       </c>
       <c r="O52">
-        <v>5.256843700000001</v>
+        <v>5.075700574000001</v>
       </c>
       <c r="P52">
-        <v>25.6657663</v>
+        <v>24.781361626</v>
       </c>
       <c r="Q52">
-        <v>41.06576629999999</v>
+        <v>40.18136162599999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1282209375063877</v>
+        <v>0.1297467405203344</v>
       </c>
       <c r="T52">
-        <v>1.903485854650985</v>
+        <v>1.938723799545829</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.580407748953168</v>
+        <v>1.549419361718792</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6118,22 +6118,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1016729028549638</v>
+        <v>0.1018853369567339</v>
       </c>
       <c r="C53">
-        <v>416.8316923755506</v>
+        <v>402.3261082472045</v>
       </c>
       <c r="D53">
-        <v>828.9421123755507</v>
+        <v>826.2759482472046</v>
       </c>
       <c r="E53">
-        <v>603.66842</v>
+        <v>615.50784</v>
       </c>
       <c r="F53">
-        <v>603.81042</v>
+        <v>615.64984</v>
       </c>
       <c r="G53">
         <v>191.7</v>
@@ -6154,28 +6154,28 @@
         <v>84.2</v>
       </c>
       <c r="M53">
-        <v>54.3429378</v>
+        <v>55.4084856</v>
       </c>
       <c r="N53">
-        <v>29.8570622</v>
+        <v>28.7915144</v>
       </c>
       <c r="O53">
-        <v>5.075700574000001</v>
+        <v>4.894557448000001</v>
       </c>
       <c r="P53">
-        <v>24.781361626</v>
+        <v>23.896956952</v>
       </c>
       <c r="Q53">
-        <v>40.18136162599999</v>
+        <v>39.296956952</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1297467405203344</v>
+        <v>0.1313361186598622</v>
       </c>
       <c r="T53">
-        <v>1.938723799545829</v>
+        <v>1.975429992144625</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.549419361718792</v>
+        <v>1.519622835531892</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6200,22 +6200,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1018853369567339</v>
+        <v>0.1285693526624014</v>
       </c>
       <c r="C54">
-        <v>402.3261082472045</v>
+        <v>152.7231497670189</v>
       </c>
       <c r="D54">
-        <v>826.2759482472046</v>
+        <v>588.512409767019</v>
       </c>
       <c r="E54">
-        <v>615.50784</v>
+        <v>627.34726</v>
       </c>
       <c r="F54">
-        <v>615.64984</v>
+        <v>627.4892600000001</v>
       </c>
       <c r="G54">
         <v>191.7</v>
@@ -6236,45 +6236,45 @@
         <v>84.2</v>
       </c>
       <c r="M54">
-        <v>55.4084856</v>
+        <v>92.11542336800002</v>
       </c>
       <c r="N54">
-        <v>28.7915144</v>
+        <v>-7.91542336800002</v>
       </c>
       <c r="O54">
-        <v>4.894557448000001</v>
+        <v>-1.345621972560004</v>
       </c>
       <c r="P54">
-        <v>23.896956952</v>
+        <v>-6.569801395440017</v>
       </c>
       <c r="Q54">
-        <v>39.296956952</v>
+        <v>8.830198604559975</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1313361186598622</v>
+        <v>0.1337350466848791</v>
       </c>
       <c r="T54">
-        <v>1.975429992144625</v>
+        <v>2.030832486948709</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.17</v>
+        <v>0.155392001432982</v>
       </c>
       <c r="W54">
-        <v>0.07469999999999999</v>
+        <v>0.1239884541896383</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.519622835531892</v>
+        <v>0.9140705966645999</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6282,22 +6282,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1285693526624014</v>
+        <v>0.1295793526624015</v>
       </c>
       <c r="C55">
-        <v>152.7231497670189</v>
+        <v>134.5429687888761</v>
       </c>
       <c r="D55">
-        <v>588.512409767019</v>
+        <v>582.1716487888762</v>
       </c>
       <c r="E55">
-        <v>627.34726</v>
+        <v>639.18668</v>
       </c>
       <c r="F55">
-        <v>627.4892600000001</v>
+        <v>639.3286800000001</v>
       </c>
       <c r="G55">
         <v>191.7</v>
@@ -6318,37 +6318,37 @@
         <v>84.2</v>
       </c>
       <c r="M55">
-        <v>92.11542336800002</v>
+        <v>93.85345022400001</v>
       </c>
       <c r="N55">
-        <v>-7.91542336800002</v>
+        <v>-9.653450224000011</v>
       </c>
       <c r="O55">
-        <v>-1.345621972560004</v>
+        <v>-1.641086538080002</v>
       </c>
       <c r="P55">
-        <v>-6.569801395440017</v>
+        <v>-8.012363685920009</v>
       </c>
       <c r="Q55">
-        <v>8.830198604559975</v>
+        <v>7.387636314079982</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1337350466848791</v>
+        <v>0.1356466781345504</v>
       </c>
       <c r="T55">
-        <v>2.030832486948709</v>
+        <v>2.074981019273681</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.155392001432982</v>
+        <v>0.1525143717768156</v>
       </c>
       <c r="W55">
-        <v>0.1239884541896383</v>
+        <v>0.1244108902231635</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9140705966645999</v>
+        <v>0.8971433633930332</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6364,22 +6364,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1295793526624015</v>
+        <v>0.1305893526624015</v>
       </c>
       <c r="C56">
-        <v>134.5429687888761</v>
+        <v>116.4979648653723</v>
       </c>
       <c r="D56">
-        <v>582.1716487888762</v>
+        <v>575.9660648653723</v>
       </c>
       <c r="E56">
-        <v>639.18668</v>
+        <v>651.0261</v>
       </c>
       <c r="F56">
-        <v>639.3286800000001</v>
+        <v>651.1681000000001</v>
       </c>
       <c r="G56">
         <v>191.7</v>
@@ -6400,37 +6400,37 @@
         <v>84.2</v>
       </c>
       <c r="M56">
-        <v>93.85345022400001</v>
+        <v>95.59147708000002</v>
       </c>
       <c r="N56">
-        <v>-9.653450224000011</v>
+        <v>-11.39147708000002</v>
       </c>
       <c r="O56">
-        <v>-1.641086538080002</v>
+        <v>-1.936551103600003</v>
       </c>
       <c r="P56">
-        <v>-8.012363685920009</v>
+        <v>-9.454925976400013</v>
       </c>
       <c r="Q56">
-        <v>7.387636314079982</v>
+        <v>5.945074023599979</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1356466781345504</v>
+        <v>0.1376432709819848</v>
       </c>
       <c r="T56">
-        <v>2.074981019273681</v>
+        <v>2.121091708590873</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1525143717768156</v>
+        <v>0.1497413831990554</v>
       </c>
       <c r="W56">
-        <v>0.1244108902231635</v>
+        <v>0.1248179649463787</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8971433633930332</v>
+        <v>0.8808316658767963</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6446,22 +6446,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1305893526624015</v>
+        <v>0.1315993526624015</v>
       </c>
       <c r="C57">
-        <v>116.4979648653723</v>
+        <v>98.5838608805152</v>
       </c>
       <c r="D57">
-        <v>575.9660648653723</v>
+        <v>569.8913808805154</v>
       </c>
       <c r="E57">
-        <v>651.0261</v>
+        <v>662.8655200000001</v>
       </c>
       <c r="F57">
-        <v>651.1681000000001</v>
+        <v>663.0075200000001</v>
       </c>
       <c r="G57">
         <v>191.7</v>
@@ -6482,37 +6482,37 @@
         <v>84.2</v>
       </c>
       <c r="M57">
-        <v>95.59147708000002</v>
+        <v>97.32950393600002</v>
       </c>
       <c r="N57">
-        <v>-11.39147708000002</v>
+        <v>-13.12950393600002</v>
       </c>
       <c r="O57">
-        <v>-1.936551103600003</v>
+        <v>-2.232015669120003</v>
       </c>
       <c r="P57">
-        <v>-9.454925976400013</v>
+        <v>-10.89748826688002</v>
       </c>
       <c r="Q57">
-        <v>5.945074023599979</v>
+        <v>4.502511733119974</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1376432709819848</v>
+        <v>0.1397306180497572</v>
       </c>
       <c r="T57">
-        <v>2.121091708590873</v>
+        <v>2.169298338331575</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1497413831990554</v>
+        <v>0.1470674299276437</v>
       </c>
       <c r="W57">
-        <v>0.1248179649463787</v>
+        <v>0.1252105012866219</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8808316658767963</v>
+        <v>0.8651025289861392</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6528,22 +6528,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1315993526624015</v>
+        <v>0.1326093526624015</v>
       </c>
       <c r="C58">
-        <v>98.5838608805152</v>
+        <v>80.79655827713827</v>
       </c>
       <c r="D58">
-        <v>569.8913808805154</v>
+        <v>563.9434982771384</v>
       </c>
       <c r="E58">
-        <v>662.8655200000001</v>
+        <v>674.7049400000001</v>
       </c>
       <c r="F58">
-        <v>663.0075200000001</v>
+        <v>674.8469400000001</v>
       </c>
       <c r="G58">
         <v>191.7</v>
@@ -6564,37 +6564,37 @@
         <v>84.2</v>
       </c>
       <c r="M58">
-        <v>97.32950393600002</v>
+        <v>99.06753079200003</v>
       </c>
       <c r="N58">
-        <v>-13.12950393600002</v>
+        <v>-14.86753079200003</v>
       </c>
       <c r="O58">
-        <v>-2.232015669120003</v>
+        <v>-2.527480234640004</v>
       </c>
       <c r="P58">
-        <v>-10.89748826688002</v>
+        <v>-12.34005055736002</v>
       </c>
       <c r="Q58">
-        <v>4.502511733119974</v>
+        <v>3.05994944263997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1397306180497572</v>
+        <v>0.1419150510276586</v>
       </c>
       <c r="T58">
-        <v>2.169298338331575</v>
+        <v>2.219747136897426</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1470674299276437</v>
+        <v>0.1444872995780359</v>
       </c>
       <c r="W58">
-        <v>0.1252105012866219</v>
+        <v>0.1255892644219443</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8651025289861392</v>
+        <v>0.8499252916355051</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6610,22 +6610,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1326093526624015</v>
+        <v>0.1336193526624014</v>
       </c>
       <c r="C59">
-        <v>80.79655827713827</v>
+        <v>63.13212783516803</v>
       </c>
       <c r="D59">
-        <v>563.9434982771384</v>
+        <v>558.1184878351681</v>
       </c>
       <c r="E59">
-        <v>674.7049400000001</v>
+        <v>686.54436</v>
       </c>
       <c r="F59">
-        <v>674.8469400000001</v>
+        <v>686.68636</v>
       </c>
       <c r="G59">
         <v>191.7</v>
@@ -6646,37 +6646,37 @@
         <v>84.2</v>
       </c>
       <c r="M59">
-        <v>99.06753079200003</v>
+        <v>100.805557648</v>
       </c>
       <c r="N59">
-        <v>-14.86753079200003</v>
+        <v>-16.60555764800002</v>
       </c>
       <c r="O59">
-        <v>-2.527480234640004</v>
+        <v>-2.822944800160003</v>
       </c>
       <c r="P59">
-        <v>-12.34005055736002</v>
+        <v>-13.78261284784001</v>
       </c>
       <c r="Q59">
-        <v>3.05994944263997</v>
+        <v>1.617387152159978</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1419150510276586</v>
+        <v>0.1442035046235552</v>
       </c>
       <c r="T59">
-        <v>2.219747136897426</v>
+        <v>2.272598259204507</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1444872995780359</v>
+        <v>0.1419961392404835</v>
       </c>
       <c r="W59">
-        <v>0.1255892644219443</v>
+        <v>0.125954966759497</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8499252916355051</v>
+        <v>0.835271407296962</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6692,22 +6692,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1336193526624014</v>
+        <v>0.1346293526624014</v>
       </c>
       <c r="C60">
-        <v>63.13212783516815</v>
+        <v>45.58680101556274</v>
       </c>
       <c r="D60">
-        <v>558.1184878351681</v>
+        <v>552.4125810155628</v>
       </c>
       <c r="E60">
-        <v>686.5443599999999</v>
+        <v>698.3837799999999</v>
       </c>
       <c r="F60">
-        <v>686.6863599999999</v>
+        <v>698.5257799999999</v>
       </c>
       <c r="G60">
         <v>191.7</v>
@@ -6728,37 +6728,37 @@
         <v>84.2</v>
       </c>
       <c r="M60">
-        <v>100.805557648</v>
+        <v>102.543584504</v>
       </c>
       <c r="N60">
-        <v>-16.605557648</v>
+        <v>-18.34358450399999</v>
       </c>
       <c r="O60">
-        <v>-2.822944800160001</v>
+        <v>-3.118409365679999</v>
       </c>
       <c r="P60">
-        <v>-13.78261284784</v>
+        <v>-15.22517513831999</v>
       </c>
       <c r="Q60">
-        <v>1.61738715215999</v>
+        <v>0.1748248616799977</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1442035046235552</v>
+        <v>0.1466035901021784</v>
       </c>
       <c r="T60">
-        <v>2.272598259204507</v>
+        <v>2.328027485038763</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1419961392404835</v>
+        <v>0.1395894250160686</v>
       </c>
       <c r="W60">
-        <v>0.125954966759497</v>
+        <v>0.1263082724076411</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.835271407296962</v>
+        <v>0.8211142648004035</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6774,22 +6774,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1346293526624014</v>
+        <v>0.1356393526624015</v>
       </c>
       <c r="C61">
-        <v>45.58680101556274</v>
+        <v>28.15696182984743</v>
       </c>
       <c r="D61">
-        <v>552.4125810155628</v>
+        <v>546.8221618298475</v>
       </c>
       <c r="E61">
-        <v>698.3837799999999</v>
+        <v>710.2231999999999</v>
       </c>
       <c r="F61">
-        <v>698.5257799999999</v>
+        <v>710.3652</v>
       </c>
       <c r="G61">
         <v>191.7</v>
@@ -6810,37 +6810,37 @@
         <v>84.2</v>
       </c>
       <c r="M61">
-        <v>102.543584504</v>
+        <v>104.28161136</v>
       </c>
       <c r="N61">
-        <v>-18.34358450399999</v>
+        <v>-20.08161136</v>
       </c>
       <c r="O61">
-        <v>-3.118409365679999</v>
+        <v>-3.413873931199999</v>
       </c>
       <c r="P61">
-        <v>-15.22517513831999</v>
+        <v>-16.6677374288</v>
       </c>
       <c r="Q61">
-        <v>0.1748248616799977</v>
+        <v>-1.267737428800004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1466035901021784</v>
+        <v>0.1491236798547329</v>
       </c>
       <c r="T61">
-        <v>2.328027485038763</v>
+        <v>2.386228172164732</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1395894250160686</v>
+        <v>0.1372629345991341</v>
       </c>
       <c r="W61">
-        <v>0.1263082724076411</v>
+        <v>0.1266498012008471</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8211142648004035</v>
+        <v>0.8074290270537301</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6856,22 +6856,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1356393526624015</v>
+        <v>0.1705868713527957</v>
       </c>
       <c r="C62">
-        <v>28.15696182984743</v>
+        <v>-125.501404928043</v>
       </c>
       <c r="D62">
-        <v>546.8221618298475</v>
+        <v>405.0032150719569</v>
       </c>
       <c r="E62">
-        <v>710.2231999999999</v>
+        <v>722.0626199999999</v>
       </c>
       <c r="F62">
-        <v>710.3652</v>
+        <v>722.20462</v>
       </c>
       <c r="G62">
         <v>191.7</v>
@@ -6892,45 +6892,45 @@
         <v>84.2</v>
       </c>
       <c r="M62">
-        <v>104.28161136</v>
+        <v>145.018687696</v>
       </c>
       <c r="N62">
-        <v>-20.08161136</v>
+        <v>-60.818687696</v>
       </c>
       <c r="O62">
-        <v>-3.413873931199999</v>
+        <v>-10.33917690832</v>
       </c>
       <c r="P62">
-        <v>-16.6677374288</v>
+        <v>-50.47951078768</v>
       </c>
       <c r="Q62">
-        <v>-1.267737428800004</v>
+        <v>-35.07951078768001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1491236798547329</v>
+        <v>0.1543307452109935</v>
       </c>
       <c r="T62">
-        <v>2.386228172164732</v>
+        <v>2.506483723117633</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1372629345991341</v>
+        <v>0.09870452027538806</v>
       </c>
       <c r="W62">
-        <v>0.1266498012008471</v>
+        <v>0.1809801323287021</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8074290270537301</v>
+        <v>0.5806148251493415</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6938,22 +6938,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1705868713527957</v>
+        <v>0.1721368713527958</v>
       </c>
       <c r="C63">
-        <v>-125.501404928043</v>
+        <v>-141.9465168339783</v>
       </c>
       <c r="D63">
-        <v>405.0032150719569</v>
+        <v>400.3975231660217</v>
       </c>
       <c r="E63">
-        <v>722.0626199999999</v>
+        <v>733.9020399999999</v>
       </c>
       <c r="F63">
-        <v>722.20462</v>
+        <v>734.04404</v>
       </c>
       <c r="G63">
         <v>191.7</v>
@@ -6974,37 +6974,37 @@
         <v>84.2</v>
       </c>
       <c r="M63">
-        <v>145.018687696</v>
+        <v>147.396043232</v>
       </c>
       <c r="N63">
-        <v>-60.818687696</v>
+        <v>-63.19604323200001</v>
       </c>
       <c r="O63">
-        <v>-10.33917690832</v>
+        <v>-10.74332734944</v>
       </c>
       <c r="P63">
-        <v>-50.47951078768</v>
+        <v>-52.45271588256001</v>
       </c>
       <c r="Q63">
-        <v>-35.07951078768001</v>
+        <v>-37.05271588256002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1543307452109935</v>
+        <v>0.1571868174533881</v>
       </c>
       <c r="T63">
-        <v>2.506483723117633</v>
+        <v>2.572443821094413</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09870452027538806</v>
+        <v>0.09711251188384955</v>
       </c>
       <c r="W63">
-        <v>0.1809801323287021</v>
+        <v>0.181299807613723</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5806148251493415</v>
+        <v>0.5712500699049973</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7020,22 +7020,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1721368713527958</v>
+        <v>0.1736868713527957</v>
       </c>
       <c r="C64">
-        <v>-141.9465168339783</v>
+        <v>-158.2880548304058</v>
       </c>
       <c r="D64">
-        <v>400.3975231660217</v>
+        <v>395.8954051695941</v>
       </c>
       <c r="E64">
-        <v>733.9020399999999</v>
+        <v>745.74146</v>
       </c>
       <c r="F64">
-        <v>734.04404</v>
+        <v>745.88346</v>
       </c>
       <c r="G64">
         <v>191.7</v>
@@ -7056,37 +7056,37 @@
         <v>84.2</v>
       </c>
       <c r="M64">
-        <v>147.396043232</v>
+        <v>149.773398768</v>
       </c>
       <c r="N64">
-        <v>-63.19604323200001</v>
+        <v>-65.57339876800002</v>
       </c>
       <c r="O64">
-        <v>-10.74332734944</v>
+        <v>-11.14747779056</v>
       </c>
       <c r="P64">
-        <v>-52.45271588256001</v>
+        <v>-54.42592097744001</v>
       </c>
       <c r="Q64">
-        <v>-37.05271588256002</v>
+        <v>-39.02592097744002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1571868174533881</v>
+        <v>0.1601972719791553</v>
       </c>
       <c r="T64">
-        <v>2.572443821094413</v>
+        <v>2.64196932977264</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09711251188384955</v>
+        <v>0.09557104344124875</v>
       </c>
       <c r="W64">
-        <v>0.181299807613723</v>
+        <v>0.1816093344769973</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5712500699049973</v>
+        <v>0.5621826084779338</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7102,22 +7102,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1736868713527957</v>
+        <v>0.1752368713527958</v>
       </c>
       <c r="C65">
-        <v>-158.2880548304058</v>
+        <v>-174.5294738620671</v>
       </c>
       <c r="D65">
-        <v>395.8954051695941</v>
+        <v>391.493406137933</v>
       </c>
       <c r="E65">
-        <v>745.74146</v>
+        <v>757.58088</v>
       </c>
       <c r="F65">
-        <v>745.88346</v>
+        <v>757.72288</v>
       </c>
       <c r="G65">
         <v>191.7</v>
@@ -7138,37 +7138,37 @@
         <v>84.2</v>
       </c>
       <c r="M65">
-        <v>149.773398768</v>
+        <v>152.150754304</v>
       </c>
       <c r="N65">
-        <v>-65.57339876800002</v>
+        <v>-67.950754304</v>
       </c>
       <c r="O65">
-        <v>-11.14747779056</v>
+        <v>-11.55162823168</v>
       </c>
       <c r="P65">
-        <v>-54.42592097744001</v>
+        <v>-56.39912607232</v>
       </c>
       <c r="Q65">
-        <v>-39.02592097744002</v>
+        <v>-40.99912607232001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1601972719791553</v>
+        <v>0.1633749739785763</v>
       </c>
       <c r="T65">
-        <v>2.64196932977264</v>
+        <v>2.715357366710769</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09557104344124875</v>
+        <v>0.09407774588747923</v>
       </c>
       <c r="W65">
-        <v>0.1816093344769973</v>
+        <v>0.1819091886257942</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5621826084779338</v>
+        <v>0.5533985052204662</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7184,22 +7184,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1752368713527958</v>
+        <v>0.1767868713527957</v>
       </c>
       <c r="C66">
-        <v>-174.5294738620671</v>
+        <v>-190.6740769000626</v>
       </c>
       <c r="D66">
-        <v>391.493406137933</v>
+        <v>387.1882230999374</v>
       </c>
       <c r="E66">
-        <v>757.58088</v>
+        <v>769.4203</v>
       </c>
       <c r="F66">
-        <v>757.72288</v>
+        <v>769.5623000000001</v>
       </c>
       <c r="G66">
         <v>191.7</v>
@@ -7220,37 +7220,37 @@
         <v>84.2</v>
       </c>
       <c r="M66">
-        <v>152.150754304</v>
+        <v>154.52810984</v>
       </c>
       <c r="N66">
-        <v>-67.950754304</v>
+        <v>-70.32810984000001</v>
       </c>
       <c r="O66">
-        <v>-11.55162823168</v>
+        <v>-11.9557786728</v>
       </c>
       <c r="P66">
-        <v>-56.39912607232</v>
+        <v>-58.37233116720001</v>
       </c>
       <c r="Q66">
-        <v>-40.99912607232001</v>
+        <v>-42.97233116720002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1633749739785763</v>
+        <v>0.1667342589493928</v>
       </c>
       <c r="T66">
-        <v>2.715357366710769</v>
+        <v>2.792939005759648</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09407774588747923</v>
+        <v>0.09263039595074879</v>
       </c>
       <c r="W66">
-        <v>0.1819091886257942</v>
+        <v>0.1821998164930896</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5533985052204662</v>
+        <v>0.5448846820632282</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7266,22 +7266,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1767868713527957</v>
+        <v>0.1783368713527957</v>
       </c>
       <c r="C67">
-        <v>-190.6740769000626</v>
+        <v>-206.7250232070969</v>
       </c>
       <c r="D67">
-        <v>387.1882230999374</v>
+        <v>382.9766967929032</v>
       </c>
       <c r="E67">
-        <v>769.4203</v>
+        <v>781.25972</v>
       </c>
       <c r="F67">
-        <v>769.5623000000001</v>
+        <v>781.4017200000001</v>
       </c>
       <c r="G67">
         <v>191.7</v>
@@ -7302,37 +7302,37 @@
         <v>84.2</v>
       </c>
       <c r="M67">
-        <v>154.52810984</v>
+        <v>156.905465376</v>
       </c>
       <c r="N67">
-        <v>-70.32810984000001</v>
+        <v>-72.70546537600002</v>
       </c>
       <c r="O67">
-        <v>-11.9557786728</v>
+        <v>-12.35992911392001</v>
       </c>
       <c r="P67">
-        <v>-58.37233116720001</v>
+        <v>-60.34553626208002</v>
       </c>
       <c r="Q67">
-        <v>-42.97233116720002</v>
+        <v>-44.94553626208003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1667342589493928</v>
+        <v>0.1702911489184926</v>
       </c>
       <c r="T67">
-        <v>2.792939005759648</v>
+        <v>2.875084270634932</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09263039595074879</v>
+        <v>0.09122690510301015</v>
       </c>
       <c r="W67">
-        <v>0.1821998164930896</v>
+        <v>0.1824816374553156</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5448846820632282</v>
+        <v>0.5366288535471186</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7348,22 +7348,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1783368713527957</v>
+        <v>0.1798868713527957</v>
       </c>
       <c r="C68">
-        <v>-206.7250232070969</v>
+        <v>-222.6853360691086</v>
       </c>
       <c r="D68">
-        <v>382.9766967929032</v>
+        <v>378.8558039308914</v>
       </c>
       <c r="E68">
-        <v>781.25972</v>
+        <v>793.09914</v>
       </c>
       <c r="F68">
-        <v>781.4017200000001</v>
+        <v>793.2411400000001</v>
       </c>
       <c r="G68">
         <v>191.7</v>
@@ -7384,37 +7384,37 @@
         <v>84.2</v>
       </c>
       <c r="M68">
-        <v>156.905465376</v>
+        <v>159.282820912</v>
       </c>
       <c r="N68">
-        <v>-72.70546537600002</v>
+        <v>-75.08282091200003</v>
       </c>
       <c r="O68">
-        <v>-12.35992911392001</v>
+        <v>-12.76407955504001</v>
       </c>
       <c r="P68">
-        <v>-60.34553626208002</v>
+        <v>-62.31874135696003</v>
       </c>
       <c r="Q68">
-        <v>-44.94553626208003</v>
+        <v>-46.91874135696003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1702911489184926</v>
+        <v>0.1740636079766287</v>
       </c>
       <c r="T68">
-        <v>2.875084270634932</v>
+        <v>2.962208036411748</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09122690510301015</v>
+        <v>0.08986530950445777</v>
       </c>
       <c r="W68">
-        <v>0.1824816374553156</v>
+        <v>0.1827550458515049</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5366288535471186</v>
+        <v>0.5286194676732809</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7430,22 +7430,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1798868713527957</v>
+        <v>0.1814368713527957</v>
       </c>
       <c r="C69">
-        <v>-222.6853360691086</v>
+        <v>-238.5579100330544</v>
       </c>
       <c r="D69">
-        <v>378.8558039308914</v>
+        <v>374.8226499669456</v>
       </c>
       <c r="E69">
-        <v>793.09914</v>
+        <v>804.9385600000001</v>
       </c>
       <c r="F69">
-        <v>793.2411400000001</v>
+        <v>805.0805600000001</v>
       </c>
       <c r="G69">
         <v>191.7</v>
@@ -7466,37 +7466,37 @@
         <v>84.2</v>
       </c>
       <c r="M69">
-        <v>159.282820912</v>
+        <v>161.660176448</v>
       </c>
       <c r="N69">
-        <v>-75.08282091200003</v>
+        <v>-77.46017644800001</v>
       </c>
       <c r="O69">
-        <v>-12.76407955504001</v>
+        <v>-13.16822999616</v>
       </c>
       <c r="P69">
-        <v>-62.31874135696003</v>
+        <v>-64.29194645184</v>
       </c>
       <c r="Q69">
-        <v>-46.91874135696003</v>
+        <v>-48.89194645184001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1740636079766287</v>
+        <v>0.1780718457258984</v>
       </c>
       <c r="T69">
-        <v>2.962208036411748</v>
+        <v>3.054777037549615</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08986530950445777</v>
+        <v>0.08854376083527457</v>
       </c>
       <c r="W69">
-        <v>0.1827550458515049</v>
+        <v>0.1830204128242769</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5286194676732809</v>
+        <v>0.5208456519722033</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7512,22 +7512,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1814368713527957</v>
+        <v>0.1829868713527958</v>
       </c>
       <c r="C70">
-        <v>-238.5579100330544</v>
+        <v>-254.345517687257</v>
       </c>
       <c r="D70">
-        <v>374.8226499669456</v>
+        <v>370.8744623127431</v>
       </c>
       <c r="E70">
-        <v>804.9385600000001</v>
+        <v>816.7779800000001</v>
       </c>
       <c r="F70">
-        <v>805.0805600000001</v>
+        <v>816.9199800000001</v>
       </c>
       <c r="G70">
         <v>191.7</v>
@@ -7548,37 +7548,37 @@
         <v>84.2</v>
       </c>
       <c r="M70">
-        <v>161.660176448</v>
+        <v>164.037531984</v>
       </c>
       <c r="N70">
-        <v>-77.46017644800001</v>
+        <v>-79.83753198400002</v>
       </c>
       <c r="O70">
-        <v>-13.16822999616</v>
+        <v>-13.57238043728</v>
       </c>
       <c r="P70">
-        <v>-64.29194645184</v>
+        <v>-66.26515154672002</v>
       </c>
       <c r="Q70">
-        <v>-48.89194645184001</v>
+        <v>-50.86515154672003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1780718457258984</v>
+        <v>0.1823386794589918</v>
       </c>
       <c r="T70">
-        <v>3.054777037549615</v>
+        <v>3.15331823230928</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08854376083527457</v>
+        <v>0.08726051792461843</v>
       </c>
       <c r="W70">
-        <v>0.1830204128242769</v>
+        <v>0.1832780880007366</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5208456519722033</v>
+        <v>0.5132971642624613</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7594,22 +7594,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1829868713527958</v>
+        <v>0.1845368713527958</v>
       </c>
       <c r="C71">
-        <v>-254.345517687257</v>
+        <v>-270.0508160176968</v>
       </c>
       <c r="D71">
-        <v>370.8744623127431</v>
+        <v>367.0085839823032</v>
       </c>
       <c r="E71">
-        <v>816.7779800000001</v>
+        <v>828.6174</v>
       </c>
       <c r="F71">
-        <v>816.9199800000001</v>
+        <v>828.7594</v>
       </c>
       <c r="G71">
         <v>191.7</v>
@@ -7630,37 +7630,37 @@
         <v>84.2</v>
       </c>
       <c r="M71">
-        <v>164.037531984</v>
+        <v>166.41488752</v>
       </c>
       <c r="N71">
-        <v>-79.83753198400002</v>
+        <v>-82.21488752</v>
       </c>
       <c r="O71">
-        <v>-13.57238043728</v>
+        <v>-13.9765308784</v>
       </c>
       <c r="P71">
-        <v>-66.26515154672002</v>
+        <v>-68.23835664160001</v>
       </c>
       <c r="Q71">
-        <v>-50.86515154672003</v>
+        <v>-52.83835664160001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1823386794589918</v>
+        <v>0.1868899687742916</v>
       </c>
       <c r="T71">
-        <v>3.15331823230928</v>
+        <v>3.258428840052924</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08726051792461843</v>
+        <v>0.08601393909712388</v>
       </c>
       <c r="W71">
-        <v>0.1832780880007366</v>
+        <v>0.1835284010292975</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5132971642624613</v>
+        <v>0.5059643476301404</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7676,22 +7676,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1845368713527958</v>
+        <v>0.2113393821930595</v>
       </c>
       <c r="C72">
-        <v>-270.0508160176968</v>
+        <v>-337.9393576180962</v>
       </c>
       <c r="D72">
-        <v>367.0085839823032</v>
+        <v>310.9594623819039</v>
       </c>
       <c r="E72">
-        <v>828.6174</v>
+        <v>840.45682</v>
       </c>
       <c r="F72">
-        <v>828.7594</v>
+        <v>840.59882</v>
       </c>
       <c r="G72">
         <v>191.7</v>
@@ -7712,45 +7712,45 @@
         <v>84.2</v>
       </c>
       <c r="M72">
-        <v>166.41488752</v>
+        <v>198.213201756</v>
       </c>
       <c r="N72">
-        <v>-82.21488752</v>
+        <v>-114.013201756</v>
       </c>
       <c r="O72">
-        <v>-13.9765308784</v>
+        <v>-19.38224429852</v>
       </c>
       <c r="P72">
-        <v>-68.23835664160001</v>
+        <v>-94.63095745748001</v>
       </c>
       <c r="Q72">
-        <v>-52.83835664160001</v>
+        <v>-79.23095745748002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1868899687742916</v>
+        <v>0.1931431085260386</v>
       </c>
       <c r="T72">
-        <v>3.258428840052924</v>
+        <v>3.402843153026295</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08601393909712388</v>
+        <v>0.07221516969197896</v>
       </c>
       <c r="W72">
-        <v>0.1835284010292975</v>
+        <v>0.2187716629866314</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5059643476301404</v>
+        <v>0.4247951158351703</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7758,22 +7758,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2113393821930594</v>
+        <v>0.2132393821930595</v>
       </c>
       <c r="C73">
-        <v>-337.939357618096</v>
+        <v>-353.1091903115068</v>
       </c>
       <c r="D73">
-        <v>310.9594623819039</v>
+        <v>307.6290496884931</v>
       </c>
       <c r="E73">
-        <v>840.4568199999999</v>
+        <v>852.2962399999999</v>
       </c>
       <c r="F73">
-        <v>840.5988199999999</v>
+        <v>852.43824</v>
       </c>
       <c r="G73">
         <v>191.7</v>
@@ -7794,37 +7794,37 @@
         <v>84.2</v>
       </c>
       <c r="M73">
-        <v>198.213201756</v>
+        <v>201.004936992</v>
       </c>
       <c r="N73">
-        <v>-114.013201756</v>
+        <v>-116.804936992</v>
       </c>
       <c r="O73">
-        <v>-19.38224429852</v>
+        <v>-19.85683928864</v>
       </c>
       <c r="P73">
-        <v>-94.63095745747998</v>
+        <v>-96.94809770335998</v>
       </c>
       <c r="Q73">
-        <v>-79.23095745747999</v>
+        <v>-81.54809770335999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1931431085260386</v>
+        <v>0.1984053624019685</v>
       </c>
       <c r="T73">
-        <v>3.402843153026294</v>
+        <v>3.524373265634376</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07221516969197896</v>
+        <v>0.07121218122403482</v>
       </c>
       <c r="W73">
-        <v>0.2187716629866314</v>
+        <v>0.2190081676673726</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4247951158351704</v>
+        <v>0.4188951836707929</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7840,22 +7840,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2132393821930595</v>
+        <v>0.2151393821930594</v>
       </c>
       <c r="C74">
-        <v>-353.1091903115068</v>
+        <v>-368.2084407202939</v>
       </c>
       <c r="D74">
-        <v>307.6290496884931</v>
+        <v>304.369219279706</v>
       </c>
       <c r="E74">
-        <v>852.2962399999999</v>
+        <v>864.1356599999999</v>
       </c>
       <c r="F74">
-        <v>852.43824</v>
+        <v>864.27766</v>
       </c>
       <c r="G74">
         <v>191.7</v>
@@ -7876,37 +7876,37 @@
         <v>84.2</v>
       </c>
       <c r="M74">
-        <v>201.004936992</v>
+        <v>203.796672228</v>
       </c>
       <c r="N74">
-        <v>-116.804936992</v>
+        <v>-119.596672228</v>
       </c>
       <c r="O74">
-        <v>-19.85683928864</v>
+        <v>-20.33143427876</v>
       </c>
       <c r="P74">
-        <v>-96.94809770335998</v>
+        <v>-99.26523794924</v>
       </c>
       <c r="Q74">
-        <v>-81.54809770335999</v>
+        <v>-83.86523794924001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1984053624019685</v>
+        <v>0.2040574128613007</v>
       </c>
       <c r="T74">
-        <v>3.524373265634376</v>
+        <v>3.65490560880602</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07121218122403482</v>
+        <v>0.07023667189219872</v>
       </c>
       <c r="W74">
-        <v>0.2190081676673726</v>
+        <v>0.2192381927678196</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4188951836707929</v>
+        <v>0.4131568934835218</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7922,22 +7922,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2151393821930594</v>
+        <v>0.2170393821930595</v>
       </c>
       <c r="C75">
-        <v>-368.2084407202939</v>
+        <v>-383.2393291195379</v>
       </c>
       <c r="D75">
-        <v>304.369219279706</v>
+        <v>301.1777508804621</v>
       </c>
       <c r="E75">
-        <v>864.1356599999999</v>
+        <v>875.9750799999999</v>
       </c>
       <c r="F75">
-        <v>864.27766</v>
+        <v>876.11708</v>
       </c>
       <c r="G75">
         <v>191.7</v>
@@ -7958,37 +7958,37 @@
         <v>84.2</v>
       </c>
       <c r="M75">
-        <v>203.796672228</v>
+        <v>206.588407464</v>
       </c>
       <c r="N75">
-        <v>-119.596672228</v>
+        <v>-122.388407464</v>
       </c>
       <c r="O75">
-        <v>-20.33143427876</v>
+        <v>-20.80602926888</v>
       </c>
       <c r="P75">
-        <v>-99.26523794924</v>
+        <v>-101.58237819512</v>
       </c>
       <c r="Q75">
-        <v>-83.86523794924001</v>
+        <v>-86.18237819512001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2040574128613007</v>
+        <v>0.2101442364328891</v>
       </c>
       <c r="T75">
-        <v>3.65490560880602</v>
+        <v>3.795478901452404</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07023667189219872</v>
+        <v>0.06928752767743927</v>
       </c>
       <c r="W75">
-        <v>0.2192381927678196</v>
+        <v>0.2194620009736598</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4131568934835218</v>
+        <v>0.407573692220231</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8004,22 +8004,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2170393821930595</v>
+        <v>0.2189393821930595</v>
       </c>
       <c r="C76">
-        <v>-383.2393291195379</v>
+        <v>-398.2039836277067</v>
       </c>
       <c r="D76">
-        <v>301.1777508804621</v>
+        <v>298.0525163722933</v>
       </c>
       <c r="E76">
-        <v>875.9750799999999</v>
+        <v>887.8145</v>
       </c>
       <c r="F76">
-        <v>876.11708</v>
+        <v>887.9565</v>
       </c>
       <c r="G76">
         <v>191.7</v>
@@ -8040,37 +8040,37 @@
         <v>84.2</v>
       </c>
       <c r="M76">
-        <v>206.588407464</v>
+        <v>209.3801427</v>
       </c>
       <c r="N76">
-        <v>-122.388407464</v>
+        <v>-125.1801427</v>
       </c>
       <c r="O76">
-        <v>-20.80602926888</v>
+        <v>-21.280624259</v>
       </c>
       <c r="P76">
-        <v>-101.58237819512</v>
+        <v>-103.899518441</v>
       </c>
       <c r="Q76">
-        <v>-86.18237819512001</v>
+        <v>-88.49951844100002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2101442364328891</v>
+        <v>0.2167180058902048</v>
       </c>
       <c r="T76">
-        <v>3.795478901452404</v>
+        <v>3.947298057510502</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06928752767743927</v>
+        <v>0.0683636939750734</v>
       </c>
       <c r="W76">
-        <v>0.2194620009736598</v>
+        <v>0.2196798409606777</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.407573692220231</v>
+        <v>0.4021393763239611</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8086,22 +8086,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2189393821930595</v>
+        <v>0.2208393821930594</v>
       </c>
       <c r="C77">
-        <v>-398.2039836277067</v>
+        <v>-413.1044449389628</v>
       </c>
       <c r="D77">
-        <v>298.0525163722933</v>
+        <v>294.9914750610372</v>
       </c>
       <c r="E77">
-        <v>887.8145</v>
+        <v>899.65392</v>
       </c>
       <c r="F77">
-        <v>887.9565</v>
+        <v>899.79592</v>
       </c>
       <c r="G77">
         <v>191.7</v>
@@ -8122,37 +8122,37 @@
         <v>84.2</v>
       </c>
       <c r="M77">
-        <v>209.3801427</v>
+        <v>212.171877936</v>
       </c>
       <c r="N77">
-        <v>-125.1801427</v>
+        <v>-127.971877936</v>
       </c>
       <c r="O77">
-        <v>-21.280624259</v>
+        <v>-21.75521924912</v>
       </c>
       <c r="P77">
-        <v>-103.899518441</v>
+        <v>-106.21665868688</v>
       </c>
       <c r="Q77">
-        <v>-88.49951844100002</v>
+        <v>-90.81665868688002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2167180058902048</v>
+        <v>0.2238395894689633</v>
       </c>
       <c r="T77">
-        <v>3.947298057510502</v>
+        <v>4.111768809906772</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0683636939750734</v>
+        <v>0.06746417168592771</v>
       </c>
       <c r="W77">
-        <v>0.2196798409606777</v>
+        <v>0.2198919483164583</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4021393763239611</v>
+        <v>0.3968480687407512</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8168,22 +8168,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2208393821930594</v>
+        <v>0.2227393821930595</v>
       </c>
       <c r="C78">
-        <v>-413.1044449389628</v>
+        <v>-427.9426707668268</v>
       </c>
       <c r="D78">
-        <v>294.9914750610372</v>
+        <v>291.9926692331732</v>
       </c>
       <c r="E78">
-        <v>899.65392</v>
+        <v>911.49334</v>
       </c>
       <c r="F78">
-        <v>899.79592</v>
+        <v>911.63534</v>
       </c>
       <c r="G78">
         <v>191.7</v>
@@ -8204,37 +8204,37 @@
         <v>84.2</v>
       </c>
       <c r="M78">
-        <v>212.171877936</v>
+        <v>214.963613172</v>
       </c>
       <c r="N78">
-        <v>-127.971877936</v>
+        <v>-130.763613172</v>
       </c>
       <c r="O78">
-        <v>-21.75521924912</v>
+        <v>-22.22981423924001</v>
       </c>
       <c r="P78">
-        <v>-106.21665868688</v>
+        <v>-108.53379893276</v>
       </c>
       <c r="Q78">
-        <v>-90.81665868688002</v>
+        <v>-93.13379893276003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2238395894689633</v>
+        <v>0.2315804411850051</v>
       </c>
       <c r="T78">
-        <v>4.111768809906772</v>
+        <v>4.290541366859241</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06746417168592771</v>
+        <v>0.06658801361208448</v>
       </c>
       <c r="W78">
-        <v>0.2198919483164583</v>
+        <v>0.2200985463902705</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3968480687407512</v>
+        <v>0.391694197718144</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8250,22 +8250,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2227393821930595</v>
+        <v>0.2246393821930594</v>
       </c>
       <c r="C79">
-        <v>-427.9426707668268</v>
+        <v>-442.7205400195272</v>
       </c>
       <c r="D79">
-        <v>291.9926692331732</v>
+        <v>289.0542199804729</v>
       </c>
       <c r="E79">
-        <v>911.49334</v>
+        <v>923.33276</v>
       </c>
       <c r="F79">
-        <v>911.63534</v>
+        <v>923.4747600000001</v>
       </c>
       <c r="G79">
         <v>191.7</v>
@@ -8286,37 +8286,37 @@
         <v>84.2</v>
       </c>
       <c r="M79">
-        <v>214.963613172</v>
+        <v>217.755348408</v>
       </c>
       <c r="N79">
-        <v>-130.763613172</v>
+        <v>-133.555348408</v>
       </c>
       <c r="O79">
-        <v>-22.22981423924001</v>
+        <v>-22.70440922936001</v>
       </c>
       <c r="P79">
-        <v>-108.53379893276</v>
+        <v>-110.85093917864</v>
       </c>
       <c r="Q79">
-        <v>-93.13379893276003</v>
+        <v>-95.45093917864004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2315804411850051</v>
+        <v>0.2400250066934145</v>
       </c>
       <c r="T79">
-        <v>4.290541366859241</v>
+        <v>4.485565974443752</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06658801361208448</v>
+        <v>0.06573432112987827</v>
       </c>
       <c r="W79">
-        <v>0.2200985463902705</v>
+        <v>0.2202998470775747</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.391694197718144</v>
+        <v>0.386672477234578</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8332,22 +8332,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2246393821930594</v>
+        <v>0.2265393821930595</v>
       </c>
       <c r="C80">
-        <v>-442.7205400195272</v>
+        <v>-457.4398567257549</v>
       </c>
       <c r="D80">
-        <v>289.0542199804729</v>
+        <v>286.1743232742452</v>
       </c>
       <c r="E80">
-        <v>923.33276</v>
+        <v>935.17218</v>
       </c>
       <c r="F80">
-        <v>923.4747600000001</v>
+        <v>935.3141800000001</v>
       </c>
       <c r="G80">
         <v>191.7</v>
@@ -8368,37 +8368,37 @@
         <v>84.2</v>
       </c>
       <c r="M80">
-        <v>217.755348408</v>
+        <v>220.547083644</v>
       </c>
       <c r="N80">
-        <v>-133.555348408</v>
+        <v>-136.347083644</v>
       </c>
       <c r="O80">
-        <v>-22.70440922936001</v>
+        <v>-23.17900421948</v>
       </c>
       <c r="P80">
-        <v>-110.85093917864</v>
+        <v>-113.16807942452</v>
       </c>
       <c r="Q80">
-        <v>-95.45093917864004</v>
+        <v>-97.76807942452001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2400250066934145</v>
+        <v>0.249273816535958</v>
       </c>
       <c r="T80">
-        <v>4.485565974443752</v>
+        <v>4.699164354179168</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06573432112987827</v>
+        <v>0.06490224111557602</v>
       </c>
       <c r="W80">
-        <v>0.2202998470775747</v>
+        <v>0.2204960515449472</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.386672477234578</v>
+        <v>0.3817778889151531</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8414,22 +8414,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2265393821930595</v>
+        <v>0.2284393821930595</v>
       </c>
       <c r="C81">
-        <v>-457.4398567257549</v>
+        <v>-472.1023537280531</v>
       </c>
       <c r="D81">
-        <v>286.1743232742452</v>
+        <v>283.351246271947</v>
       </c>
       <c r="E81">
-        <v>935.17218</v>
+        <v>947.0116</v>
       </c>
       <c r="F81">
-        <v>935.3141800000001</v>
+        <v>947.1536000000001</v>
       </c>
       <c r="G81">
         <v>191.7</v>
@@ -8450,37 +8450,37 @@
         <v>84.2</v>
       </c>
       <c r="M81">
-        <v>220.547083644</v>
+        <v>223.33881888</v>
       </c>
       <c r="N81">
-        <v>-136.347083644</v>
+        <v>-139.13881888</v>
       </c>
       <c r="O81">
-        <v>-23.17900421948</v>
+        <v>-23.65359920960001</v>
       </c>
       <c r="P81">
-        <v>-113.16807942452</v>
+        <v>-115.4852196704</v>
       </c>
       <c r="Q81">
-        <v>-97.76807942452001</v>
+        <v>-100.0852196704</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.249273816535958</v>
+        <v>0.259447507362756</v>
       </c>
       <c r="T81">
-        <v>4.699164354179168</v>
+        <v>4.934122571888127</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06490224111557602</v>
+        <v>0.06409096310163132</v>
       </c>
       <c r="W81">
-        <v>0.2204960515449472</v>
+        <v>0.2206873509006353</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3817778889151531</v>
+        <v>0.3770056653037136</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8496,22 +8496,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2284393821930595</v>
+        <v>0.2303393821930595</v>
       </c>
       <c r="C82">
-        <v>-472.1023537280531</v>
+        <v>-486.7096961597338</v>
       </c>
       <c r="D82">
-        <v>283.351246271947</v>
+        <v>280.5833238402664</v>
       </c>
       <c r="E82">
-        <v>947.0116</v>
+        <v>958.8510200000001</v>
       </c>
       <c r="F82">
-        <v>947.1536000000001</v>
+        <v>958.9930200000001</v>
       </c>
       <c r="G82">
         <v>191.7</v>
@@ -8532,37 +8532,37 @@
         <v>84.2</v>
       </c>
       <c r="M82">
-        <v>223.33881888</v>
+        <v>226.130554116</v>
       </c>
       <c r="N82">
-        <v>-139.13881888</v>
+        <v>-141.9305541160001</v>
       </c>
       <c r="O82">
-        <v>-23.65359920960001</v>
+        <v>-24.12819419972001</v>
       </c>
       <c r="P82">
-        <v>-115.4852196704</v>
+        <v>-117.80235991628</v>
       </c>
       <c r="Q82">
-        <v>-100.0852196704</v>
+        <v>-102.40235991628</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.259447507362756</v>
+        <v>0.2706921130134273</v>
       </c>
       <c r="T82">
-        <v>4.934122571888127</v>
+        <v>5.193813233566451</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06409096310163132</v>
+        <v>0.06329971664358648</v>
       </c>
       <c r="W82">
-        <v>0.2206873509006353</v>
+        <v>0.2208739268154423</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3770056653037136</v>
+        <v>0.372351274374038</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8578,22 +8578,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2303393821930595</v>
+        <v>0.2322393821930595</v>
       </c>
       <c r="C83">
-        <v>-486.7096961597338</v>
+        <v>-501.2634847199802</v>
       </c>
       <c r="D83">
-        <v>280.5833238402664</v>
+        <v>277.8689552800199</v>
       </c>
       <c r="E83">
-        <v>958.8510200000001</v>
+        <v>970.6904400000001</v>
       </c>
       <c r="F83">
-        <v>958.9930200000001</v>
+        <v>970.8324400000001</v>
       </c>
       <c r="G83">
         <v>191.7</v>
@@ -8614,37 +8614,37 @@
         <v>84.2</v>
       </c>
       <c r="M83">
-        <v>226.130554116</v>
+        <v>228.922289352</v>
       </c>
       <c r="N83">
-        <v>-141.9305541160001</v>
+        <v>-144.722289352</v>
       </c>
       <c r="O83">
-        <v>-24.12819419972001</v>
+        <v>-24.60278918984001</v>
       </c>
       <c r="P83">
-        <v>-117.80235991628</v>
+        <v>-120.11950016216</v>
       </c>
       <c r="Q83">
-        <v>-102.40235991628</v>
+        <v>-104.71950016216</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2706921130134273</v>
+        <v>0.2831861192919511</v>
       </c>
       <c r="T83">
-        <v>5.193813233566451</v>
+        <v>5.482358413209032</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06329971664358648</v>
+        <v>0.0625277688796403</v>
       </c>
       <c r="W83">
-        <v>0.2208739268154423</v>
+        <v>0.2210559520981808</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.372351274374038</v>
+        <v>0.3678104051743548</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8660,22 +8660,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2322393821930595</v>
+        <v>0.2341393821930595</v>
       </c>
       <c r="C84">
-        <v>-501.2634847199802</v>
+        <v>-515.7652587606701</v>
       </c>
       <c r="D84">
-        <v>277.8689552800199</v>
+        <v>275.20660123933</v>
       </c>
       <c r="E84">
-        <v>970.6904400000001</v>
+        <v>982.52986</v>
       </c>
       <c r="F84">
-        <v>970.8324400000001</v>
+        <v>982.67186</v>
       </c>
       <c r="G84">
         <v>191.7</v>
@@ -8696,37 +8696,37 @@
         <v>84.2</v>
       </c>
       <c r="M84">
-        <v>228.922289352</v>
+        <v>231.714024588</v>
       </c>
       <c r="N84">
-        <v>-144.722289352</v>
+        <v>-147.514024588</v>
       </c>
       <c r="O84">
-        <v>-24.60278918984001</v>
+        <v>-25.07738417996001</v>
       </c>
       <c r="P84">
-        <v>-120.11950016216</v>
+        <v>-122.43664040804</v>
       </c>
       <c r="Q84">
-        <v>-104.71950016216</v>
+        <v>-107.03664040804</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2831861192919511</v>
+        <v>0.2971500086620659</v>
       </c>
       <c r="T84">
-        <v>5.482358413209032</v>
+        <v>5.804850084574269</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0625277688796403</v>
+        <v>0.06177442226663259</v>
       </c>
       <c r="W84">
-        <v>0.2210559520981808</v>
+        <v>0.221233591229528</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3678104051743548</v>
+        <v>0.3633789545096034</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8742,22 +8742,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2341393821930595</v>
+        <v>0.2360393821930595</v>
       </c>
       <c r="C85">
-        <v>-515.7652587606701</v>
+        <v>-530.2164991974272</v>
       </c>
       <c r="D85">
-        <v>275.20660123933</v>
+        <v>272.5947808025729</v>
       </c>
       <c r="E85">
-        <v>982.52986</v>
+        <v>994.36928</v>
       </c>
       <c r="F85">
-        <v>982.67186</v>
+        <v>994.5112800000001</v>
       </c>
       <c r="G85">
         <v>191.7</v>
@@ -8778,37 +8778,37 @@
         <v>84.2</v>
       </c>
       <c r="M85">
-        <v>231.714024588</v>
+        <v>234.505759824</v>
       </c>
       <c r="N85">
-        <v>-147.514024588</v>
+        <v>-150.305759824</v>
       </c>
       <c r="O85">
-        <v>-25.07738417996001</v>
+        <v>-25.55197917008</v>
       </c>
       <c r="P85">
-        <v>-122.43664040804</v>
+        <v>-124.75378065392</v>
       </c>
       <c r="Q85">
-        <v>-107.03664040804</v>
+        <v>-109.35378065392</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2971500086620659</v>
+        <v>0.3128593842034451</v>
       </c>
       <c r="T85">
-        <v>5.804850084574269</v>
+        <v>6.167653214860162</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06177442226663259</v>
+        <v>0.06103901247774411</v>
       </c>
       <c r="W85">
-        <v>0.221233591229528</v>
+        <v>0.2214070008577479</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3633789545096034</v>
+        <v>0.3590530145749654</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8824,22 +8824,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2360393821930595</v>
+        <v>0.2379393821930595</v>
       </c>
       <c r="C86">
-        <v>-530.2164991974271</v>
+        <v>-544.6186312564697</v>
       </c>
       <c r="D86">
-        <v>272.5947808025729</v>
+        <v>270.0320687435303</v>
       </c>
       <c r="E86">
-        <v>994.3692799999999</v>
+        <v>1006.2087</v>
       </c>
       <c r="F86">
-        <v>994.5112799999999</v>
+        <v>1006.3507</v>
       </c>
       <c r="G86">
         <v>191.7</v>
@@ -8860,37 +8860,37 @@
         <v>84.2</v>
       </c>
       <c r="M86">
-        <v>234.505759824</v>
+        <v>237.29749506</v>
       </c>
       <c r="N86">
-        <v>-150.305759824</v>
+        <v>-153.09749506</v>
       </c>
       <c r="O86">
-        <v>-25.55197917008</v>
+        <v>-26.0265741602</v>
       </c>
       <c r="P86">
-        <v>-124.75378065392</v>
+        <v>-127.0709208998</v>
       </c>
       <c r="Q86">
-        <v>-109.35378065392</v>
+        <v>-111.6709208998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3128593842034449</v>
+        <v>0.3306633431503412</v>
       </c>
       <c r="T86">
-        <v>6.167653214860158</v>
+        <v>6.578830095850835</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06103901247774413</v>
+        <v>0.06032090644859419</v>
       </c>
       <c r="W86">
-        <v>0.2214070008577479</v>
+        <v>0.2215763302594215</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3590530145749653</v>
+        <v>0.3548288614623188</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8906,22 +8906,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2379393821930595</v>
+        <v>0.2398393821930595</v>
       </c>
       <c r="C87">
-        <v>-544.6186312564697</v>
+        <v>-558.9730270679599</v>
       </c>
       <c r="D87">
-        <v>270.0320687435303</v>
+        <v>267.51709293204</v>
       </c>
       <c r="E87">
-        <v>1006.2087</v>
+        <v>1018.04812</v>
       </c>
       <c r="F87">
-        <v>1006.3507</v>
+        <v>1018.19012</v>
       </c>
       <c r="G87">
         <v>191.7</v>
@@ -8942,37 +8942,37 @@
         <v>84.2</v>
       </c>
       <c r="M87">
-        <v>237.29749506</v>
+        <v>240.089230296</v>
       </c>
       <c r="N87">
-        <v>-153.09749506</v>
+        <v>-155.889230296</v>
       </c>
       <c r="O87">
-        <v>-26.0265741602</v>
+        <v>-26.50116915032</v>
       </c>
       <c r="P87">
-        <v>-127.0709208998</v>
+        <v>-129.38806114568</v>
       </c>
       <c r="Q87">
-        <v>-111.6709208998</v>
+        <v>-113.98806114568</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3306633431503412</v>
+        <v>0.351010724803937</v>
       </c>
       <c r="T87">
-        <v>6.578830095850835</v>
+        <v>7.048746531268752</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06032090644859419</v>
+        <v>0.05961950055965704</v>
       </c>
       <c r="W87">
-        <v>0.2215763302594215</v>
+        <v>0.2217417217680329</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3548288614623188</v>
+        <v>0.3507029444685709</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8988,22 +8988,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2398393821930595</v>
+        <v>0.2417393821930594</v>
       </c>
       <c r="C88">
-        <v>-558.9730270679599</v>
+        <v>-573.28100811577</v>
       </c>
       <c r="D88">
-        <v>267.51709293204</v>
+        <v>265.04853188423</v>
       </c>
       <c r="E88">
-        <v>1018.04812</v>
+        <v>1029.88754</v>
       </c>
       <c r="F88">
-        <v>1018.19012</v>
+        <v>1030.02954</v>
       </c>
       <c r="G88">
         <v>191.7</v>
@@ -9024,37 +9024,37 @@
         <v>84.2</v>
       </c>
       <c r="M88">
-        <v>240.089230296</v>
+        <v>242.880965532</v>
       </c>
       <c r="N88">
-        <v>-155.889230296</v>
+        <v>-158.680965532</v>
       </c>
       <c r="O88">
-        <v>-26.50116915032</v>
+        <v>-26.97576414044001</v>
       </c>
       <c r="P88">
-        <v>-129.38806114568</v>
+        <v>-131.70520139156</v>
       </c>
       <c r="Q88">
-        <v>-113.98806114568</v>
+        <v>-116.30520139156</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.351010724803937</v>
+        <v>0.3744884728657782</v>
       </c>
       <c r="T88">
-        <v>7.048746531268752</v>
+        <v>7.590957802904809</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05961950055965704</v>
+        <v>0.0589342189440288</v>
       </c>
       <c r="W88">
-        <v>0.2217417217680329</v>
+        <v>0.221903311172998</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3507029444685709</v>
+        <v>0.3466718761413459</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9070,22 +9070,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2417393821930594</v>
+        <v>0.2436393821930595</v>
       </c>
       <c r="C89">
-        <v>-573.28100811577</v>
+        <v>-587.5438475528542</v>
       </c>
       <c r="D89">
-        <v>265.04853188423</v>
+        <v>262.6251124471459</v>
       </c>
       <c r="E89">
-        <v>1029.88754</v>
+        <v>1041.72696</v>
       </c>
       <c r="F89">
-        <v>1030.02954</v>
+        <v>1041.86896</v>
       </c>
       <c r="G89">
         <v>191.7</v>
@@ -9106,37 +9106,37 @@
         <v>84.2</v>
       </c>
       <c r="M89">
-        <v>242.880965532</v>
+        <v>245.672700768</v>
       </c>
       <c r="N89">
-        <v>-158.680965532</v>
+        <v>-161.472700768</v>
       </c>
       <c r="O89">
-        <v>-26.97576414044001</v>
+        <v>-27.45035913056001</v>
       </c>
       <c r="P89">
-        <v>-131.70520139156</v>
+        <v>-134.02234163744</v>
       </c>
       <c r="Q89">
-        <v>-116.30520139156</v>
+        <v>-118.62234163744</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3744884728657782</v>
+        <v>0.4018791789379265</v>
       </c>
       <c r="T89">
-        <v>7.590957802904809</v>
+        <v>8.223537619813545</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0589342189440288</v>
+        <v>0.05826451191057393</v>
       </c>
       <c r="W89">
-        <v>0.221903311172998</v>
+        <v>0.2220612280914867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3466718761413459</v>
+        <v>0.3427324230033759</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9152,22 +9152,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2436393821930595</v>
+        <v>0.2455393821930594</v>
       </c>
       <c r="C90">
-        <v>-587.5438475528542</v>
+        <v>-601.7627723907511</v>
       </c>
       <c r="D90">
-        <v>262.6251124471459</v>
+        <v>260.2456076092489</v>
       </c>
       <c r="E90">
-        <v>1041.72696</v>
+        <v>1053.56638</v>
       </c>
       <c r="F90">
-        <v>1041.86896</v>
+        <v>1053.70838</v>
       </c>
       <c r="G90">
         <v>191.7</v>
@@ -9188,37 +9188,37 @@
         <v>84.2</v>
       </c>
       <c r="M90">
-        <v>245.672700768</v>
+        <v>248.464436004</v>
       </c>
       <c r="N90">
-        <v>-161.472700768</v>
+        <v>-164.264436004</v>
       </c>
       <c r="O90">
-        <v>-27.45035913056001</v>
+        <v>-27.92495412068</v>
       </c>
       <c r="P90">
-        <v>-134.02234163744</v>
+        <v>-136.33948188332</v>
       </c>
       <c r="Q90">
-        <v>-118.62234163744</v>
+        <v>-120.93948188332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4018791789379265</v>
+        <v>0.4342500133868289</v>
       </c>
       <c r="T90">
-        <v>8.223537619813545</v>
+        <v>8.971131948887503</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05826451191057393</v>
+        <v>0.05760985447337647</v>
       </c>
       <c r="W90">
-        <v>0.2220612280914867</v>
+        <v>0.2222155963151778</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3427324230033759</v>
+        <v>0.3388814969022146</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9234,22 +9234,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2455393821930594</v>
+        <v>0.2474393821930594</v>
       </c>
       <c r="C91">
-        <v>-601.7627723907511</v>
+        <v>-615.9389655711277</v>
       </c>
       <c r="D91">
-        <v>260.2456076092489</v>
+        <v>257.9088344288723</v>
       </c>
       <c r="E91">
-        <v>1053.56638</v>
+        <v>1065.4058</v>
       </c>
       <c r="F91">
-        <v>1053.70838</v>
+        <v>1065.5478</v>
       </c>
       <c r="G91">
         <v>191.7</v>
@@ -9270,37 +9270,37 @@
         <v>84.2</v>
       </c>
       <c r="M91">
-        <v>248.464436004</v>
+        <v>251.25617124</v>
       </c>
       <c r="N91">
-        <v>-164.264436004</v>
+        <v>-167.05617124</v>
       </c>
       <c r="O91">
-        <v>-27.92495412068</v>
+        <v>-28.39954911080001</v>
       </c>
       <c r="P91">
-        <v>-136.33948188332</v>
+        <v>-138.6566221292</v>
       </c>
       <c r="Q91">
-        <v>-120.93948188332</v>
+        <v>-123.2566221292</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4342500133868289</v>
+        <v>0.4730950147255119</v>
       </c>
       <c r="T91">
-        <v>8.971131948887503</v>
+        <v>9.868245143776255</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05760985447337647</v>
+        <v>0.05696974497922784</v>
       </c>
       <c r="W91">
-        <v>0.2222155963151778</v>
+        <v>0.2223665341338981</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3388814969022146</v>
+        <v>0.3351161469366343</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2474393821930594</v>
+        <v>0.2493393821930595</v>
       </c>
       <c r="C92">
-        <v>-615.9389655711277</v>
+        <v>-630.0735679267118</v>
       </c>
       <c r="D92">
-        <v>257.9088344288723</v>
+        <v>255.6136520732883</v>
       </c>
       <c r="E92">
-        <v>1065.4058</v>
+        <v>1077.24522</v>
       </c>
       <c r="F92">
-        <v>1065.5478</v>
+        <v>1077.38722</v>
       </c>
       <c r="G92">
         <v>191.7</v>
@@ -9352,37 +9352,37 @@
         <v>84.2</v>
       </c>
       <c r="M92">
-        <v>251.25617124</v>
+        <v>254.047906476</v>
       </c>
       <c r="N92">
-        <v>-167.05617124</v>
+        <v>-169.847906476</v>
       </c>
       <c r="O92">
-        <v>-28.39954911080001</v>
+        <v>-28.87414410092001</v>
       </c>
       <c r="P92">
-        <v>-138.6566221292</v>
+        <v>-140.97376237508</v>
       </c>
       <c r="Q92">
-        <v>-123.2566221292</v>
+        <v>-125.5737623750801</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4730950147255119</v>
+        <v>0.5205722385839022</v>
       </c>
       <c r="T92">
-        <v>9.868245143776255</v>
+        <v>10.96471682641806</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05696974497922784</v>
+        <v>0.05634370382560995</v>
       </c>
       <c r="W92">
-        <v>0.2223665341338981</v>
+        <v>0.2225141546379212</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3351161469366343</v>
+        <v>0.3314335519153525</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9398,22 +9398,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2493393821930595</v>
+        <v>0.2512393821930595</v>
       </c>
       <c r="C93">
-        <v>-630.0735679267118</v>
+        <v>-644.1676800384442</v>
       </c>
       <c r="D93">
-        <v>255.6136520732883</v>
+        <v>253.3589599615559</v>
       </c>
       <c r="E93">
-        <v>1077.24522</v>
+        <v>1089.08464</v>
       </c>
       <c r="F93">
-        <v>1077.38722</v>
+        <v>1089.22664</v>
       </c>
       <c r="G93">
         <v>191.7</v>
@@ -9434,37 +9434,37 @@
         <v>84.2</v>
       </c>
       <c r="M93">
-        <v>254.047906476</v>
+        <v>256.8396417120001</v>
       </c>
       <c r="N93">
-        <v>-169.847906476</v>
+        <v>-172.6396417120001</v>
       </c>
       <c r="O93">
-        <v>-28.87414410092001</v>
+        <v>-29.34873909104001</v>
       </c>
       <c r="P93">
-        <v>-140.97376237508</v>
+        <v>-143.2909026209601</v>
       </c>
       <c r="Q93">
-        <v>-125.5737623750801</v>
+        <v>-127.8909026209601</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5205722385839022</v>
+        <v>0.5799187684068901</v>
       </c>
       <c r="T93">
-        <v>10.96471682641806</v>
+        <v>12.33530642972032</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05634370382560995</v>
+        <v>0.0557312722622881</v>
       </c>
       <c r="W93">
-        <v>0.2225141546379212</v>
+        <v>0.2226585660005525</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3314335519153525</v>
+        <v>0.3278310133075769</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9480,22 +9480,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2512393821930595</v>
+        <v>0.2531393821930594</v>
       </c>
       <c r="C94">
-        <v>-644.1676800384442</v>
+        <v>-658.2223639952026</v>
       </c>
       <c r="D94">
-        <v>253.3589599615559</v>
+        <v>251.1436960047975</v>
       </c>
       <c r="E94">
-        <v>1089.08464</v>
+        <v>1100.92406</v>
       </c>
       <c r="F94">
-        <v>1089.22664</v>
+        <v>1101.06606</v>
       </c>
       <c r="G94">
         <v>191.7</v>
@@ -9516,37 +9516,37 @@
         <v>84.2</v>
       </c>
       <c r="M94">
-        <v>256.8396417120001</v>
+        <v>259.631376948</v>
       </c>
       <c r="N94">
-        <v>-172.6396417120001</v>
+        <v>-175.431376948</v>
       </c>
       <c r="O94">
-        <v>-29.34873909104001</v>
+        <v>-29.82333408116001</v>
       </c>
       <c r="P94">
-        <v>-143.2909026209601</v>
+        <v>-145.60804286684</v>
       </c>
       <c r="Q94">
-        <v>-127.8909026209601</v>
+        <v>-130.2080428668401</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5799187684068901</v>
+        <v>0.6562214496078744</v>
       </c>
       <c r="T94">
-        <v>12.33530642972032</v>
+        <v>14.09749306253751</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0557312722622881</v>
+        <v>0.05513201127022049</v>
       </c>
       <c r="W94">
-        <v>0.2226585660005525</v>
+        <v>0.222799871742482</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3278310133075769</v>
+        <v>0.3243059486483557</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9562,22 +9562,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2531393821930594</v>
+        <v>0.2550393821930595</v>
       </c>
       <c r="C95">
-        <v>-658.2223639952026</v>
+        <v>-672.2386450620071</v>
       </c>
       <c r="D95">
-        <v>251.1436960047975</v>
+        <v>248.9668349379931</v>
       </c>
       <c r="E95">
-        <v>1100.92406</v>
+        <v>1112.76348</v>
       </c>
       <c r="F95">
-        <v>1101.06606</v>
+        <v>1112.90548</v>
       </c>
       <c r="G95">
         <v>191.7</v>
@@ -9598,37 +9598,37 @@
         <v>84.2</v>
       </c>
       <c r="M95">
-        <v>259.631376948</v>
+        <v>262.423112184</v>
       </c>
       <c r="N95">
-        <v>-175.431376948</v>
+        <v>-178.2231121840001</v>
       </c>
       <c r="O95">
-        <v>-29.82333408116001</v>
+        <v>-30.29792907128001</v>
       </c>
       <c r="P95">
-        <v>-145.60804286684</v>
+        <v>-147.92518311272</v>
       </c>
       <c r="Q95">
-        <v>-130.2080428668401</v>
+        <v>-132.5251831127201</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6562214496078744</v>
+        <v>0.7579583578758536</v>
       </c>
       <c r="T95">
-        <v>14.09749306253751</v>
+        <v>16.4470752396271</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05513201127022049</v>
+        <v>0.05454550051202665</v>
       </c>
       <c r="W95">
-        <v>0.222799871742482</v>
+        <v>0.2229381709792641</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3243059486483557</v>
+        <v>0.3208558853648625</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9644,22 +9644,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2550393821930595</v>
+        <v>0.2569393821930595</v>
       </c>
       <c r="C96">
-        <v>-672.2386450620071</v>
+        <v>-686.2175132622131</v>
       </c>
       <c r="D96">
-        <v>248.9668349379931</v>
+        <v>246.8273867377871</v>
       </c>
       <c r="E96">
-        <v>1112.76348</v>
+        <v>1124.6029</v>
       </c>
       <c r="F96">
-        <v>1112.90548</v>
+        <v>1124.7449</v>
       </c>
       <c r="G96">
         <v>191.7</v>
@@ -9680,37 +9680,37 @@
         <v>84.2</v>
       </c>
       <c r="M96">
-        <v>262.423112184</v>
+        <v>265.2148474200001</v>
       </c>
       <c r="N96">
-        <v>-178.2231121840001</v>
+        <v>-181.0148474200001</v>
       </c>
       <c r="O96">
-        <v>-30.29792907128001</v>
+        <v>-30.77252406140002</v>
       </c>
       <c r="P96">
-        <v>-147.92518311272</v>
+        <v>-150.2423233586001</v>
       </c>
       <c r="Q96">
-        <v>-132.5251831127201</v>
+        <v>-134.8423233586001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7579583578758536</v>
+        <v>0.900390029451025</v>
       </c>
       <c r="T96">
-        <v>16.4470752396271</v>
+        <v>19.73649028755254</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05454550051202665</v>
+        <v>0.05397133734874216</v>
       </c>
       <c r="W96">
-        <v>0.2229381709792641</v>
+        <v>0.2230735586531666</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3208558853648625</v>
+        <v>0.3174784549926009</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9726,22 +9726,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2569393821930595</v>
+        <v>0.2588393821930595</v>
       </c>
       <c r="C97">
-        <v>-686.2175132622131</v>
+        <v>-700.1599248788229</v>
       </c>
       <c r="D97">
-        <v>246.8273867377871</v>
+        <v>244.7243951211773</v>
       </c>
       <c r="E97">
-        <v>1124.6029</v>
+        <v>1136.44232</v>
       </c>
       <c r="F97">
-        <v>1124.7449</v>
+        <v>1136.58432</v>
       </c>
       <c r="G97">
         <v>191.7</v>
@@ -9762,37 +9762,37 @@
         <v>84.2</v>
       </c>
       <c r="M97">
-        <v>265.2148474200001</v>
+        <v>268.006582656</v>
       </c>
       <c r="N97">
-        <v>-181.0148474200001</v>
+        <v>-183.806582656</v>
       </c>
       <c r="O97">
-        <v>-30.77252406140002</v>
+        <v>-31.24711905152001</v>
       </c>
       <c r="P97">
-        <v>-150.2423233586001</v>
+        <v>-152.55946360448</v>
       </c>
       <c r="Q97">
-        <v>-134.8423233586001</v>
+        <v>-137.15946360448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.900390029451025</v>
+        <v>1.114037536813782</v>
       </c>
       <c r="T97">
-        <v>19.73649028755254</v>
+        <v>24.67061285944068</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05397133734874216</v>
+        <v>0.0534091359180261</v>
       </c>
       <c r="W97">
-        <v>0.2230735586531666</v>
+        <v>0.2232061257505294</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3174784549926009</v>
+        <v>0.3141713877530946</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9808,22 +9808,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2588393821930595</v>
+        <v>0.2607393821930595</v>
       </c>
       <c r="C98">
-        <v>-700.1599248788227</v>
+        <v>-714.0668038796967</v>
       </c>
       <c r="D98">
-        <v>244.7243951211773</v>
+        <v>242.6569361203032</v>
       </c>
       <c r="E98">
-        <v>1136.44232</v>
+        <v>1148.28174</v>
       </c>
       <c r="F98">
-        <v>1136.58432</v>
+        <v>1148.42374</v>
       </c>
       <c r="G98">
         <v>191.7</v>
@@ -9844,37 +9844,37 @@
         <v>84.2</v>
       </c>
       <c r="M98">
-        <v>268.006582656</v>
+        <v>270.798317892</v>
       </c>
       <c r="N98">
-        <v>-183.806582656</v>
+        <v>-186.598317892</v>
       </c>
       <c r="O98">
-        <v>-31.24711905152</v>
+        <v>-31.72171404164001</v>
       </c>
       <c r="P98">
-        <v>-152.55946360448</v>
+        <v>-154.87660385036</v>
       </c>
       <c r="Q98">
-        <v>-137.15946360448</v>
+        <v>-139.47660385036</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.114037536813779</v>
+        <v>1.470116715751705</v>
       </c>
       <c r="T98">
-        <v>24.67061285944061</v>
+        <v>32.89415047925415</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05340913591802611</v>
+        <v>0.05285852626938665</v>
       </c>
       <c r="W98">
-        <v>0.2232061257505294</v>
+        <v>0.2233359595056786</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3141713877530947</v>
+        <v>0.3109325074669803</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9890,22 +9890,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2607393821930595</v>
+        <v>0.2626393821930594</v>
       </c>
       <c r="C99">
-        <v>-714.0668038796967</v>
+        <v>-727.9390432711273</v>
       </c>
       <c r="D99">
-        <v>242.6569361203032</v>
+        <v>240.6241167288727</v>
       </c>
       <c r="E99">
-        <v>1148.28174</v>
+        <v>1160.12116</v>
       </c>
       <c r="F99">
-        <v>1148.42374</v>
+        <v>1160.26316</v>
       </c>
       <c r="G99">
         <v>191.7</v>
@@ -9926,37 +9926,37 @@
         <v>84.2</v>
       </c>
       <c r="M99">
-        <v>270.798317892</v>
+        <v>273.590053128</v>
       </c>
       <c r="N99">
-        <v>-186.598317892</v>
+        <v>-189.390053128</v>
       </c>
       <c r="O99">
-        <v>-31.72171404164001</v>
+        <v>-32.19630903176001</v>
       </c>
       <c r="P99">
-        <v>-154.87660385036</v>
+        <v>-157.19374409624</v>
       </c>
       <c r="Q99">
-        <v>-139.47660385036</v>
+        <v>-141.7937440962401</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.470116715751705</v>
+        <v>2.182275073627557</v>
       </c>
       <c r="T99">
-        <v>32.89415047925415</v>
+        <v>49.34122571888123</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05285852626938665</v>
+        <v>0.0523191535523521</v>
       </c>
       <c r="W99">
-        <v>0.2233359595056786</v>
+        <v>0.2234631435923554</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3109325074669803</v>
+        <v>0.3077597267785417</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9972,22 +9972,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2626393821930594</v>
+        <v>0.2645393821930594</v>
       </c>
       <c r="C100">
-        <v>-727.9390432711273</v>
+        <v>-741.7775063839432</v>
       </c>
       <c r="D100">
-        <v>240.6241167288727</v>
+        <v>238.6250736160568</v>
       </c>
       <c r="E100">
-        <v>1160.12116</v>
+        <v>1171.96058</v>
       </c>
       <c r="F100">
-        <v>1160.26316</v>
+        <v>1172.10258</v>
       </c>
       <c r="G100">
         <v>191.7</v>
@@ -10008,37 +10008,37 @@
         <v>84.2</v>
       </c>
       <c r="M100">
-        <v>273.590053128</v>
+        <v>276.381788364</v>
       </c>
       <c r="N100">
-        <v>-189.390053128</v>
+        <v>-192.181788364</v>
       </c>
       <c r="O100">
-        <v>-32.19630903176001</v>
+        <v>-32.67090402188001</v>
       </c>
       <c r="P100">
-        <v>-157.19374409624</v>
+        <v>-159.51088434212</v>
       </c>
       <c r="Q100">
-        <v>-141.7937440962401</v>
+        <v>-144.11088434212</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.182275073627557</v>
+        <v>4.318750147255114</v>
       </c>
       <c r="T100">
-        <v>49.34122571888123</v>
+        <v>98.68245143776245</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0523191535523521</v>
+        <v>0.0517906772538435</v>
       </c>
       <c r="W100">
-        <v>0.2234631435923554</v>
+        <v>0.2235877583035437</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10046,91 +10046,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3077597267785417</v>
+        <v>0.3046510426696676</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2645393821930594</v>
-      </c>
-      <c r="C101">
-        <v>-741.7775063839432</v>
-      </c>
-      <c r="D101">
-        <v>238.6250736160568</v>
-      </c>
-      <c r="E101">
-        <v>1171.96058</v>
-      </c>
-      <c r="F101">
-        <v>1172.10258</v>
-      </c>
-      <c r="G101">
-        <v>191.7</v>
-      </c>
-      <c r="H101">
-        <v>1183.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="K101">
-        <v>15.39999999999999</v>
-      </c>
-      <c r="L101">
-        <v>84.2</v>
-      </c>
-      <c r="M101">
-        <v>276.381788364</v>
-      </c>
-      <c r="N101">
-        <v>-192.181788364</v>
-      </c>
-      <c r="O101">
-        <v>-32.67090402188001</v>
-      </c>
-      <c r="P101">
-        <v>-159.51088434212</v>
-      </c>
-      <c r="Q101">
-        <v>-144.11088434212</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.318750147255114</v>
-      </c>
-      <c r="T101">
-        <v>98.68245143776245</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0517906772538435</v>
-      </c>
-      <c r="W101">
-        <v>0.2235877583035437</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3046510426696676</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
